--- a/docs/d/80/inyear.xlsx
+++ b/docs/d/80/inyear.xlsx
@@ -12,7 +12,7 @@
     <sheet name="By Area" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Club Health'!$A$1:$AC$218</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Club Health'!$A$1:$AC$219</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'By Area'!$A$1:$I$46</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 22-Sep-2026. Built 2026-09-23 09:04 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
         </is>
       </c>
     </row>
@@ -588,7 +588,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 38 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 39 clubs short</t>
         </is>
       </c>
     </row>
@@ -647,7 +647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC218"/>
+  <dimension ref="A1:AC219"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -8462,7 +8462,7 @@
         </is>
       </c>
       <c r="E76" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F76" s="6" t="n">
         <v>10</v>
@@ -8476,13 +8476,13 @@
         </is>
       </c>
       <c r="I76" s="4" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J76" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K76" s="4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L76" s="4" t="inlineStr">
         <is>
@@ -8520,8 +8520,8 @@
       <c r="U76" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="V76" s="9" t="n">
-        <v>0</v>
+      <c r="V76" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W76" s="9" t="n">
         <v>0</v>
@@ -10664,7 +10664,7 @@
         </is>
       </c>
       <c r="P97" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q97" s="9" t="n">
         <v>0</v>
@@ -11387,7 +11387,7 @@
         </is>
       </c>
       <c r="P104" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q104" s="9" t="n">
         <v>0</v>
@@ -16288,13 +16288,13 @@
         </is>
       </c>
       <c r="I152" s="4" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J152" s="4" t="n">
         <v>34</v>
       </c>
       <c r="K152" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L152" s="4" t="inlineStr">
         <is>
@@ -16336,7 +16336,7 @@
         <v>4</v>
       </c>
       <c r="W152" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X152" s="10" t="n">
         <v>5</v>
@@ -20681,15 +20681,15 @@
         </is>
       </c>
       <c r="C195" s="4" t="n">
-        <v>5601725</v>
+        <v>28680899</v>
       </c>
       <c r="D195" s="4" t="inlineStr">
         <is>
-          <t>Telok Blangah  CC Mandarin Toastmasters Club</t>
+          <t>Hear Singapore Toastmasters Club</t>
         </is>
       </c>
       <c r="E195" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F195" s="6" t="n">
         <v>10</v>
@@ -20703,17 +20703,17 @@
         </is>
       </c>
       <c r="I195" s="4" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="J195" s="4" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="K195" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L195" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L195" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M195" s="8" t="n">
@@ -20741,33 +20741,31 @@
       <c r="S195" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T195" s="10" t="n">
-        <v>1</v>
+      <c r="T195" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U195" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V195" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W195" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X195" s="10" t="n">
-        <v>7</v>
+      <c r="X195" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y195" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z195" s="10" t="n">
-        <v>1</v>
+      <c r="Z195" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA195" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AB195" s="4" t="n">
-        <v>6</v>
-      </c>
+      <c r="AB195" s="4" t="n"/>
       <c r="AC195" s="4" t="inlineStr"/>
     </row>
     <row r="196">
@@ -20782,15 +20780,15 @@
         </is>
       </c>
       <c r="C196" s="4" t="n">
-        <v>6485408</v>
+        <v>5601725</v>
       </c>
       <c r="D196" s="4" t="inlineStr">
         <is>
-          <t>Xi Yao Mandarin</t>
+          <t>Telok Blangah  CC Mandarin Toastmasters Club</t>
         </is>
       </c>
       <c r="E196" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F196" s="6" t="n">
         <v>10</v>
@@ -20804,13 +20802,13 @@
         </is>
       </c>
       <c r="I196" s="4" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="J196" s="4" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K196" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L196" s="7" t="inlineStr">
         <is>
@@ -20842,14 +20840,14 @@
       <c r="S196" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T196" s="9" t="n">
-        <v>0</v>
+      <c r="T196" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U196" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V196" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W196" s="9" t="n">
         <v>0</v>
@@ -20860,14 +20858,14 @@
       <c r="Y196" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z196" s="9" t="n">
-        <v>0</v>
+      <c r="Z196" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA196" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB196" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AC196" s="4" t="inlineStr"/>
     </row>
@@ -20883,15 +20881,15 @@
         </is>
       </c>
       <c r="C197" s="4" t="n">
-        <v>4435381</v>
+        <v>6485408</v>
       </c>
       <c r="D197" s="4" t="inlineStr">
         <is>
-          <t>YD Toastmasters Club</t>
+          <t>Xi Yao Mandarin</t>
         </is>
       </c>
       <c r="E197" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F197" s="6" t="n">
         <v>10</v>
@@ -20905,13 +20903,13 @@
         </is>
       </c>
       <c r="I197" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J197" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="K197" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L197" s="7" t="inlineStr">
         <is>
@@ -20932,7 +20930,7 @@
         </is>
       </c>
       <c r="P197" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q197" s="9" t="n">
         <v>0</v>
@@ -20941,62 +20939,58 @@
         <v>0</v>
       </c>
       <c r="S197" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T197" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="T197" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U197" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V197" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W197" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X197" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y197" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z197" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA197" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB197" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="Y197" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z197" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA197" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB197" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC197" s="4" t="inlineStr">
-        <is>
-          <t>Distinguished</t>
-        </is>
-      </c>
+      <c r="AC197" s="4" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" s="4" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>V</t>
         </is>
       </c>
       <c r="B198" s="4" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>06</t>
         </is>
       </c>
       <c r="C198" s="4" t="n">
-        <v>28678624</v>
+        <v>4435381</v>
       </c>
       <c r="D198" s="4" t="inlineStr">
         <is>
-          <t>Adam Explorer Toastmasters Club</t>
+          <t>YD Toastmasters Club</t>
         </is>
       </c>
       <c r="E198" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F198" s="6" t="n">
         <v>10</v>
@@ -21010,17 +21004,17 @@
         </is>
       </c>
       <c r="I198" s="4" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="J198" s="4" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="K198" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L198" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+      <c r="L198" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M198" s="8" t="n">
@@ -21037,7 +21031,7 @@
         </is>
       </c>
       <c r="P198" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q198" s="9" t="n">
         <v>0</v>
@@ -21046,10 +21040,10 @@
         <v>0</v>
       </c>
       <c r="S198" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T198" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T198" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U198" s="9" t="n">
         <v>0</v>
@@ -21060,22 +21054,26 @@
       <c r="W198" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X198" s="9" t="n">
-        <v>0</v>
+      <c r="X198" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y198" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z198" s="9" t="n">
-        <v>0</v>
+      <c r="Z198" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA198" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB198" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC198" s="4" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="AC198" s="4" t="inlineStr">
+        <is>
+          <t>Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="4" t="inlineStr">
@@ -21089,15 +21087,15 @@
         </is>
       </c>
       <c r="C199" s="4" t="n">
-        <v>1232248</v>
+        <v>28678624</v>
       </c>
       <c r="D199" s="4" t="inlineStr">
         <is>
-          <t>Chong Pang Toastmasters Club</t>
+          <t>Adam Explorer Toastmasters Club</t>
         </is>
       </c>
       <c r="E199" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F199" s="6" t="n">
         <v>10</v>
@@ -21111,10 +21109,10 @@
         </is>
       </c>
       <c r="I199" s="4" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J199" s="4" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K199" s="4" t="n">
         <v>0</v>
@@ -21138,16 +21136,16 @@
         </is>
       </c>
       <c r="P199" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q199" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R199" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S199" s="10" t="n">
-        <v>2</v>
+      <c r="S199" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="T199" s="9" t="n">
         <v>0</v>
@@ -21161,14 +21159,14 @@
       <c r="W199" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X199" s="10" t="n">
-        <v>7</v>
+      <c r="X199" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y199" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z199" s="10" t="n">
-        <v>1</v>
+      <c r="Z199" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA199" s="10" t="n">
         <v>1</v>
@@ -21176,11 +21174,7 @@
       <c r="AB199" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC199" s="4" t="inlineStr">
-        <is>
-          <t>President's Distinguished</t>
-        </is>
-      </c>
+      <c r="AC199" s="4" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" s="4" t="inlineStr">
@@ -21194,15 +21188,15 @@
         </is>
       </c>
       <c r="C200" s="4" t="n">
-        <v>7702</v>
+        <v>1232248</v>
       </c>
       <c r="D200" s="4" t="inlineStr">
         <is>
-          <t>Chua Chu Kang Toastmasters Club</t>
+          <t>Chong Pang Toastmasters Club</t>
         </is>
       </c>
       <c r="E200" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F200" s="6" t="n">
         <v>10</v>
@@ -21216,13 +21210,13 @@
         </is>
       </c>
       <c r="I200" s="4" t="n">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="J200" s="4" t="n">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="K200" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L200" s="4" t="inlineStr">
         <is>
@@ -21251,17 +21245,17 @@
       <c r="R200" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S200" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T200" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U200" s="10" t="n">
-        <v>5</v>
+      <c r="S200" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T200" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U200" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V200" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W200" s="9" t="n">
         <v>0</v>
@@ -21281,7 +21275,11 @@
       <c r="AB200" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC200" s="4" t="inlineStr"/>
+      <c r="AC200" s="4" t="inlineStr">
+        <is>
+          <t>President's Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="4" t="inlineStr">
@@ -21295,15 +21293,15 @@
         </is>
       </c>
       <c r="C201" s="4" t="n">
-        <v>2548</v>
+        <v>7702</v>
       </c>
       <c r="D201" s="4" t="inlineStr">
         <is>
-          <t>Nee Soon East Toastmasters Club</t>
+          <t>Chua Chu Kang Toastmasters Club</t>
         </is>
       </c>
       <c r="E201" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F201" s="6" t="n">
         <v>10</v>
@@ -21317,10 +21315,10 @@
         </is>
       </c>
       <c r="I201" s="4" t="n">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="J201" s="4" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="K201" s="4" t="n">
         <v>2</v>
@@ -21344,10 +21342,10 @@
         </is>
       </c>
       <c r="P201" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q201" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R201" s="9" t="n">
         <v>0</v>
@@ -21355,11 +21353,11 @@
       <c r="S201" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T201" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U201" s="9" t="n">
-        <v>0</v>
+      <c r="T201" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U201" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="V201" s="9" t="n">
         <v>2</v>
@@ -21380,13 +21378,9 @@
         <v>1</v>
       </c>
       <c r="AB201" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="AC201" s="4" t="inlineStr">
-        <is>
-          <t>President's Distinguished</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="AC201" s="4" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" s="4" t="inlineStr">
@@ -21400,11 +21394,11 @@
         </is>
       </c>
       <c r="C202" s="4" t="n">
-        <v>3758978</v>
+        <v>2548</v>
       </c>
       <c r="D202" s="4" t="inlineStr">
         <is>
-          <t>Senja-Cashew Toastmasters Club</t>
+          <t>Nee Soon East Toastmasters Club</t>
         </is>
       </c>
       <c r="E202" s="5" t="n">
@@ -21422,17 +21416,17 @@
         </is>
       </c>
       <c r="I202" s="4" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="J202" s="4" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="K202" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="L202" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="L202" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M202" s="8" t="n">
@@ -21473,7 +21467,7 @@
         <v>0</v>
       </c>
       <c r="X202" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y202" s="9" t="n">
         <v>0</v>
@@ -21485,9 +21479,13 @@
         <v>1</v>
       </c>
       <c r="AB202" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC202" s="4" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="AC202" s="4" t="inlineStr">
+        <is>
+          <t>President's Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" s="4" t="inlineStr">
@@ -21497,19 +21495,19 @@
       </c>
       <c r="B203" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C203" s="4" t="n">
-        <v>6990593</v>
+        <v>3758978</v>
       </c>
       <c r="D203" s="4" t="inlineStr">
         <is>
-          <t>ACE The Place Toastmasters Club</t>
+          <t>Senja-Cashew Toastmasters Club</t>
         </is>
       </c>
       <c r="E203" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F203" s="6" t="n">
         <v>10</v>
@@ -21523,17 +21521,17 @@
         </is>
       </c>
       <c r="I203" s="4" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="J203" s="4" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="K203" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="L203" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+      <c r="L203" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M203" s="8" t="n">
@@ -21561,11 +21559,11 @@
       <c r="S203" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T203" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U203" s="10" t="n">
-        <v>1</v>
+      <c r="T203" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U203" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V203" s="9" t="n">
         <v>2</v>
@@ -21574,7 +21572,7 @@
         <v>0</v>
       </c>
       <c r="X203" s="10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y203" s="9" t="n">
         <v>0</v>
@@ -21586,7 +21584,7 @@
         <v>1</v>
       </c>
       <c r="AB203" s="4" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="AC203" s="4" t="inlineStr"/>
     </row>
@@ -21602,11 +21600,11 @@
         </is>
       </c>
       <c r="C204" s="4" t="n">
-        <v>6478</v>
+        <v>6990593</v>
       </c>
       <c r="D204" s="4" t="inlineStr">
         <is>
-          <t>Cheng San Toastmasters Club</t>
+          <t>ACE The Place Toastmasters Club</t>
         </is>
       </c>
       <c r="E204" s="5" t="n">
@@ -21624,13 +21622,13 @@
         </is>
       </c>
       <c r="I204" s="4" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J204" s="4" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="K204" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L204" s="4" t="inlineStr">
         <is>
@@ -21654,7 +21652,7 @@
         <v>0</v>
       </c>
       <c r="Q204" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R204" s="9" t="n">
         <v>0</v>
@@ -21669,13 +21667,13 @@
         <v>1</v>
       </c>
       <c r="V204" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W204" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X204" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y204" s="9" t="n">
         <v>0</v>
@@ -21687,13 +21685,9 @@
         <v>1</v>
       </c>
       <c r="AB204" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="AC204" s="4" t="inlineStr">
-        <is>
-          <t>President's Distinguished</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="AC204" s="4" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" s="4" t="inlineStr">
@@ -21707,15 +21701,15 @@
         </is>
       </c>
       <c r="C205" s="4" t="n">
-        <v>28680566</v>
+        <v>6478</v>
       </c>
       <c r="D205" s="4" t="inlineStr">
         <is>
-          <t>Comedy-Improv Toastmasters Club</t>
+          <t>Cheng San Toastmasters Club</t>
         </is>
       </c>
       <c r="E205" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F205" s="6" t="n">
         <v>10</v>
@@ -21729,13 +21723,13 @@
         </is>
       </c>
       <c r="I205" s="4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J205" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K205" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L205" s="4" t="inlineStr">
         <is>
@@ -21759,7 +21753,7 @@
         <v>0</v>
       </c>
       <c r="Q205" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R205" s="9" t="n">
         <v>0</v>
@@ -21767,20 +21761,20 @@
       <c r="S205" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T205" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U205" s="9" t="n">
-        <v>0</v>
+      <c r="T205" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U205" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V205" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W205" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X205" s="10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y205" s="9" t="n">
         <v>0</v>
@@ -21792,9 +21786,13 @@
         <v>1</v>
       </c>
       <c r="AB205" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC205" s="4" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="AC205" s="4" t="inlineStr">
+        <is>
+          <t>President's Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="4" t="inlineStr">
@@ -21808,15 +21806,15 @@
         </is>
       </c>
       <c r="C206" s="4" t="n">
-        <v>708544</v>
+        <v>28680566</v>
       </c>
       <c r="D206" s="4" t="inlineStr">
         <is>
-          <t>Grassroots Toastmasters Club</t>
+          <t>Comedy-Improv Toastmasters Club</t>
         </is>
       </c>
       <c r="E206" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F206" s="6" t="n">
         <v>10</v>
@@ -21830,17 +21828,17 @@
         </is>
       </c>
       <c r="I206" s="4" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J206" s="4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="K206" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="L206" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="L206" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M206" s="8" t="n">
@@ -21868,11 +21866,11 @@
       <c r="S206" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T206" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U206" s="10" t="n">
-        <v>1</v>
+      <c r="T206" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U206" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V206" s="9" t="n">
         <v>2</v>
@@ -21893,7 +21891,7 @@
         <v>1</v>
       </c>
       <c r="AB206" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AC206" s="4" t="inlineStr"/>
     </row>
@@ -21909,15 +21907,15 @@
         </is>
       </c>
       <c r="C207" s="4" t="n">
-        <v>1632713</v>
+        <v>708544</v>
       </c>
       <c r="D207" s="4" t="inlineStr">
         <is>
-          <t>Kebun Baru Toastmasters Club</t>
+          <t>Grassroots Toastmasters Club</t>
         </is>
       </c>
       <c r="E207" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F207" s="6" t="n">
         <v>10</v>
@@ -21931,17 +21929,17 @@
         </is>
       </c>
       <c r="I207" s="4" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="J207" s="4" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="K207" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L207" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>2</v>
+      </c>
+      <c r="L207" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M207" s="8" t="n">
@@ -21958,25 +21956,25 @@
         </is>
       </c>
       <c r="P207" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q207" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q207" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R207" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S207" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T207" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U207" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V207" s="9" t="n">
         <v>2</v>
-      </c>
-      <c r="R207" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S207" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T207" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U207" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="V207" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="W207" s="9" t="n">
         <v>0</v>
@@ -21994,7 +21992,7 @@
         <v>1</v>
       </c>
       <c r="AB207" s="4" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="AC207" s="4" t="inlineStr"/>
     </row>
@@ -22010,11 +22008,11 @@
         </is>
       </c>
       <c r="C208" s="4" t="n">
-        <v>7967939</v>
+        <v>1632713</v>
       </c>
       <c r="D208" s="4" t="inlineStr">
         <is>
-          <t>World Travelers Toastmasters Club</t>
+          <t>Kebun Baru Toastmasters Club</t>
         </is>
       </c>
       <c r="E208" s="5" t="n">
@@ -22032,13 +22030,13 @@
         </is>
       </c>
       <c r="I208" s="4" t="n">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="J208" s="4" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="K208" s="4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L208" s="4" t="inlineStr">
         <is>
@@ -22059,28 +22057,28 @@
         </is>
       </c>
       <c r="P208" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q208" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="Q208" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="R208" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S208" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T208" s="10" t="n">
         <v>1</v>
       </c>
       <c r="U208" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="V208" s="10" t="n">
-        <v>4</v>
+        <v>2</v>
+      </c>
+      <c r="V208" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="W208" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X208" s="10" t="n">
         <v>7</v>
@@ -22107,19 +22105,19 @@
       </c>
       <c r="B209" s="4" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C209" s="4" t="n">
-        <v>9479</v>
+        <v>7967939</v>
       </c>
       <c r="D209" s="4" t="inlineStr">
         <is>
-          <t>Bishan Toastmasters Club</t>
+          <t>World Travelers Toastmasters Club</t>
         </is>
       </c>
       <c r="E209" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F209" s="6" t="n">
         <v>10</v>
@@ -22133,13 +22131,13 @@
         </is>
       </c>
       <c r="I209" s="4" t="n">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="J209" s="4" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="K209" s="4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L209" s="4" t="inlineStr">
         <is>
@@ -22160,7 +22158,7 @@
         </is>
       </c>
       <c r="P209" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q209" s="9" t="n">
         <v>0</v>
@@ -22171,20 +22169,20 @@
       <c r="S209" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T209" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U209" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V209" s="9" t="n">
-        <v>3</v>
+      <c r="T209" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U209" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V209" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W209" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X209" s="10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y209" s="9" t="n">
         <v>0</v>
@@ -22196,13 +22194,9 @@
         <v>1</v>
       </c>
       <c r="AB209" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="AC209" s="4" t="inlineStr">
-        <is>
-          <t>Distinguished</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="AC209" s="4" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" s="4" t="inlineStr">
@@ -22216,11 +22210,11 @@
         </is>
       </c>
       <c r="C210" s="4" t="n">
-        <v>7511</v>
+        <v>9479</v>
       </c>
       <c r="D210" s="4" t="inlineStr">
         <is>
-          <t>Braddell Heights II Toastmasters Club</t>
+          <t>Bishan Toastmasters Club</t>
         </is>
       </c>
       <c r="E210" s="5" t="n">
@@ -22238,13 +22232,13 @@
         </is>
       </c>
       <c r="I210" s="4" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J210" s="4" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="K210" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L210" s="4" t="inlineStr">
         <is>
@@ -22265,10 +22259,10 @@
         </is>
       </c>
       <c r="P210" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q210" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R210" s="9" t="n">
         <v>0</v>
@@ -22283,13 +22277,13 @@
         <v>0</v>
       </c>
       <c r="V210" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W210" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X210" s="10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y210" s="9" t="n">
         <v>0</v>
@@ -22301,11 +22295,11 @@
         <v>1</v>
       </c>
       <c r="AB210" s="4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AC210" s="4" t="inlineStr">
         <is>
-          <t>President's Distinguished</t>
+          <t>Distinguished</t>
         </is>
       </c>
     </row>
@@ -22321,15 +22315,15 @@
         </is>
       </c>
       <c r="C211" s="4" t="n">
-        <v>7903</v>
+        <v>7511</v>
       </c>
       <c r="D211" s="4" t="inlineStr">
         <is>
-          <t>Braddell Heights Toastmasters Club</t>
+          <t>Braddell Heights II Toastmasters Club</t>
         </is>
       </c>
       <c r="E211" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F211" s="6" t="n">
         <v>10</v>
@@ -22343,17 +22337,17 @@
         </is>
       </c>
       <c r="I211" s="4" t="n">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="J211" s="4" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="K211" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L211" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>2</v>
+      </c>
+      <c r="L211" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M211" s="8" t="n">
@@ -22373,7 +22367,7 @@
         <v>0</v>
       </c>
       <c r="Q211" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R211" s="9" t="n">
         <v>0</v>
@@ -22388,27 +22382,31 @@
         <v>0</v>
       </c>
       <c r="V211" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W211" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X211" s="10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y211" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z211" s="9" t="n">
-        <v>0</v>
+      <c r="Z211" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA211" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB211" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC211" s="4" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="AC211" s="4" t="inlineStr">
+        <is>
+          <t>President's Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" s="4" t="inlineStr">
@@ -22422,15 +22420,15 @@
         </is>
       </c>
       <c r="C212" s="4" t="n">
-        <v>28675874</v>
+        <v>7903</v>
       </c>
       <c r="D212" s="4" t="inlineStr">
         <is>
-          <t>Encantada All-Ladies  TMC</t>
+          <t>Braddell Heights Toastmasters Club</t>
         </is>
       </c>
       <c r="E212" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F212" s="6" t="n">
         <v>10</v>
@@ -22444,17 +22442,17 @@
         </is>
       </c>
       <c r="I212" s="4" t="n">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="J212" s="4" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="K212" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L212" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>1</v>
+      </c>
+      <c r="L212" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M212" s="8" t="n">
@@ -22474,7 +22472,7 @@
         <v>0</v>
       </c>
       <c r="Q212" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R212" s="9" t="n">
         <v>0</v>
@@ -22482,14 +22480,14 @@
       <c r="S212" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T212" s="10" t="n">
-        <v>1</v>
+      <c r="T212" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U212" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V212" s="10" t="n">
-        <v>4</v>
+      <c r="V212" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="W212" s="9" t="n">
         <v>0</v>
@@ -22500,20 +22498,16 @@
       <c r="Y212" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z212" s="10" t="n">
-        <v>1</v>
+      <c r="Z212" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA212" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB212" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC212" s="4" t="inlineStr">
-        <is>
-          <t>Select Distinguished</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AC212" s="4" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" s="4" t="inlineStr">
@@ -22527,15 +22521,15 @@
         </is>
       </c>
       <c r="C213" s="4" t="n">
-        <v>792</v>
+        <v>28675874</v>
       </c>
       <c r="D213" s="4" t="inlineStr">
         <is>
-          <t>Thomson Toastmasters Club</t>
+          <t>Encantada All-Ladies  TMC</t>
         </is>
       </c>
       <c r="E213" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F213" s="6" t="n">
         <v>10</v>
@@ -22549,17 +22543,17 @@
         </is>
       </c>
       <c r="I213" s="4" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="J213" s="4" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="K213" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L213" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>4</v>
+      </c>
+      <c r="L213" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M213" s="8" t="n">
@@ -22579,7 +22573,7 @@
         <v>0</v>
       </c>
       <c r="Q213" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R213" s="9" t="n">
         <v>0</v>
@@ -22587,20 +22581,20 @@
       <c r="S213" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T213" s="9" t="n">
-        <v>0</v>
+      <c r="T213" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U213" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V213" s="9" t="n">
-        <v>0</v>
+      <c r="V213" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W213" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X213" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y213" s="9" t="n">
         <v>0</v>
@@ -22612,9 +22606,13 @@
         <v>1</v>
       </c>
       <c r="AB213" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC213" s="4" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="AC213" s="4" t="inlineStr">
+        <is>
+          <t>Select Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" s="4" t="inlineStr">
@@ -22624,19 +22622,19 @@
       </c>
       <c r="B214" s="4" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C214" s="4" t="n">
-        <v>1481742</v>
+        <v>792</v>
       </c>
       <c r="D214" s="4" t="inlineStr">
         <is>
-          <t>Anchorvale CC</t>
+          <t>Thomson Toastmasters Club</t>
         </is>
       </c>
       <c r="E214" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F214" s="6" t="n">
         <v>10</v>
@@ -22650,17 +22648,17 @@
         </is>
       </c>
       <c r="I214" s="4" t="n">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="J214" s="4" t="n">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="K214" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L214" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L214" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M214" s="8" t="n">
@@ -22680,13 +22678,13 @@
         <v>0</v>
       </c>
       <c r="Q214" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R214" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S214" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T214" s="9" t="n">
         <v>0</v>
@@ -22694,14 +22692,14 @@
       <c r="U214" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V214" s="10" t="n">
-        <v>4</v>
+      <c r="V214" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="W214" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X214" s="10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y214" s="9" t="n">
         <v>0</v>
@@ -22713,7 +22711,7 @@
         <v>1</v>
       </c>
       <c r="AB214" s="4" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="AC214" s="4" t="inlineStr"/>
     </row>
@@ -22729,15 +22727,15 @@
         </is>
       </c>
       <c r="C215" s="4" t="n">
-        <v>4084190</v>
+        <v>1481742</v>
       </c>
       <c r="D215" s="4" t="inlineStr">
         <is>
-          <t>Fernvale CC Toastmasters Club</t>
+          <t>Anchorvale CC</t>
         </is>
       </c>
       <c r="E215" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F215" s="6" t="n">
         <v>10</v>
@@ -22751,17 +22749,17 @@
         </is>
       </c>
       <c r="I215" s="4" t="n">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="J215" s="4" t="n">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="K215" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L215" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>5</v>
+      </c>
+      <c r="L215" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M215" s="8" t="n">
@@ -22778,7 +22776,7 @@
         </is>
       </c>
       <c r="P215" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q215" s="9" t="n">
         <v>1</v>
@@ -22787,7 +22785,7 @@
         <v>0</v>
       </c>
       <c r="S215" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T215" s="9" t="n">
         <v>0</v>
@@ -22795,14 +22793,14 @@
       <c r="U215" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V215" s="9" t="n">
-        <v>3</v>
+      <c r="V215" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W215" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X215" s="10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y215" s="9" t="n">
         <v>0</v>
@@ -22814,7 +22812,7 @@
         <v>1</v>
       </c>
       <c r="AB215" s="4" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="AC215" s="4" t="inlineStr"/>
     </row>
@@ -22830,15 +22828,15 @@
         </is>
       </c>
       <c r="C216" s="4" t="n">
-        <v>7002588</v>
+        <v>4084190</v>
       </c>
       <c r="D216" s="4" t="inlineStr">
         <is>
-          <t>Hougang Toastmasters Club</t>
+          <t>Fernvale CC Toastmasters Club</t>
         </is>
       </c>
       <c r="E216" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F216" s="6" t="n">
         <v>10</v>
@@ -22852,13 +22850,13 @@
         </is>
       </c>
       <c r="I216" s="4" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="J216" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K216" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L216" s="7" t="inlineStr">
         <is>
@@ -22879,10 +22877,10 @@
         </is>
       </c>
       <c r="P216" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q216" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R216" s="9" t="n">
         <v>0</v>
@@ -22897,7 +22895,7 @@
         <v>0</v>
       </c>
       <c r="V216" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W216" s="9" t="n">
         <v>0</v>
@@ -22908,14 +22906,14 @@
       <c r="Y216" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z216" s="9" t="n">
-        <v>0</v>
+      <c r="Z216" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA216" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB216" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AC216" s="4" t="inlineStr"/>
     </row>
@@ -22931,15 +22929,15 @@
         </is>
       </c>
       <c r="C217" s="4" t="n">
-        <v>4255</v>
+        <v>7002588</v>
       </c>
       <c r="D217" s="4" t="inlineStr">
         <is>
-          <t>Punggol Park Toastmasters Club</t>
+          <t>Hougang Toastmasters Club</t>
         </is>
       </c>
       <c r="E217" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F217" s="6" t="n">
         <v>10</v>
@@ -22953,17 +22951,17 @@
         </is>
       </c>
       <c r="I217" s="4" t="n">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="J217" s="4" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="K217" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L217" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L217" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M217" s="8" t="n">
@@ -22980,7 +22978,7 @@
         </is>
       </c>
       <c r="P217" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q217" s="9" t="n">
         <v>0</v>
@@ -22997,32 +22995,28 @@
       <c r="U217" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V217" s="10" t="n">
+      <c r="V217" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W217" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X217" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W217" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="X217" s="10" t="n">
+      <c r="Y217" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z217" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA217" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB217" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="Y217" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z217" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA217" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB217" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="AC217" s="4" t="inlineStr">
-        <is>
-          <t>President's Distinguished</t>
-        </is>
-      </c>
+      <c r="AC217" s="4" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" s="4" t="inlineStr">
@@ -23036,11 +23030,11 @@
         </is>
       </c>
       <c r="C218" s="4" t="n">
-        <v>7881096</v>
+        <v>4255</v>
       </c>
       <c r="D218" s="4" t="inlineStr">
         <is>
-          <t>Punggol West CC Toastmasters Club</t>
+          <t>Punggol Park Toastmasters Club</t>
         </is>
       </c>
       <c r="E218" s="5" t="n">
@@ -23058,13 +23052,13 @@
         </is>
       </c>
       <c r="I218" s="4" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="J218" s="4" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="K218" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L218" s="4" t="inlineStr">
         <is>
@@ -23085,7 +23079,7 @@
         </is>
       </c>
       <c r="P218" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q218" s="9" t="n">
         <v>0</v>
@@ -23106,27 +23100,132 @@
         <v>4</v>
       </c>
       <c r="W218" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="X218" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y218" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z218" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA218" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB218" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC218" s="4" t="inlineStr">
+        <is>
+          <t>President's Distinguished</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B219" s="4" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="C219" s="4" t="n">
+        <v>7881096</v>
+      </c>
+      <c r="D219" s="4" t="inlineStr">
+        <is>
+          <t>Punggol West CC Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="E219" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="X218" s="10" t="n">
+      <c r="F219" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G219" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H219" s="4" t="inlineStr">
+        <is>
+          <t>Smedley</t>
+        </is>
+      </c>
+      <c r="I219" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="J219" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="K219" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="Y218" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z218" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA218" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB218" s="4" t="n">
+      <c r="L219" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="M219" s="8" t="n">
+        <v>46446</v>
+      </c>
+      <c r="N219" s="4" t="inlineStr">
+        <is>
+          <t>Officers trained Nov-Feb</t>
+        </is>
+      </c>
+      <c r="O219" s="7" t="inlineStr">
+        <is>
+          <t>not yet</t>
+        </is>
+      </c>
+      <c r="P219" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q219" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R219" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S219" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T219" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U219" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V219" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="AC218" s="4" t="inlineStr"/>
+      <c r="W219" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="X219" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y219" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z219" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA219" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB219" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC219" s="4" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AC218"/>
+  <autoFilter ref="A1:AC219"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -23708,7 +23807,7 @@
         <v>6</v>
       </c>
       <c r="D17" t="n">
-        <v>2.83</v>
+        <v>3</v>
       </c>
       <c r="E17" t="n">
         <v>1</v>
@@ -24530,17 +24629,17 @@
         </is>
       </c>
       <c r="C42" t="n">
+        <v>7</v>
+      </c>
+      <c r="D42" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="E42" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" t="n">
         <v>6</v>
       </c>
-      <c r="D42" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="E42" t="n">
-        <v>1</v>
-      </c>
-      <c r="F42" t="n">
-        <v>5</v>
-      </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
@@ -24548,7 +24647,7 @@
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43">

--- a/docs/d/80/inyear.xlsx
+++ b/docs/d/80/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
         </is>
       </c>
     </row>
@@ -1133,7 +1133,11 @@
       <c r="AB4" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC4" s="4" t="inlineStr"/>
+      <c r="AC4" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -1541,7 +1545,11 @@
       <c r="AB8" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC8" s="4" t="inlineStr"/>
+      <c r="AC8" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -2761,7 +2769,11 @@
       <c r="AB20" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC20" s="4" t="inlineStr"/>
+      <c r="AC20" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -2967,7 +2979,11 @@
       <c r="AB22" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC22" s="4" t="inlineStr"/>
+      <c r="AC22" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
@@ -3068,7 +3084,11 @@
       <c r="AB23" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC23" s="4" t="inlineStr"/>
+      <c r="AC23" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
@@ -3169,7 +3189,11 @@
       <c r="AB24" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC24" s="4" t="inlineStr"/>
+      <c r="AC24" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
@@ -4712,7 +4736,11 @@
       <c r="AB39" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC39" s="4" t="inlineStr"/>
+      <c r="AC39" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
@@ -5536,7 +5564,11 @@
       <c r="AB47" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC47" s="4" t="inlineStr"/>
+      <c r="AC47" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
@@ -6259,7 +6291,11 @@
       <c r="AB54" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC54" s="4" t="inlineStr"/>
+      <c r="AC54" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
@@ -6570,7 +6606,11 @@
       <c r="AB57" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC57" s="4" t="inlineStr"/>
+      <c r="AC57" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
@@ -6881,7 +6921,11 @@
       <c r="AB60" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC60" s="4" t="inlineStr"/>
+      <c r="AC60" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
@@ -7192,7 +7236,11 @@
       <c r="AB63" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC63" s="4" t="inlineStr"/>
+      <c r="AC63" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
@@ -8125,7 +8173,11 @@
       <c r="AB72" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC72" s="4" t="inlineStr"/>
+      <c r="AC72" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
@@ -8541,7 +8593,11 @@
       <c r="AB76" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC76" s="4" t="inlineStr"/>
+      <c r="AC76" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
@@ -8642,7 +8698,11 @@
       <c r="AB77" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC77" s="4" t="inlineStr"/>
+      <c r="AC77" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
@@ -8743,7 +8803,11 @@
       <c r="AB78" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC78" s="4" t="inlineStr"/>
+      <c r="AC78" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
@@ -9365,7 +9429,11 @@
       <c r="AB84" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC84" s="4" t="inlineStr"/>
+      <c r="AC84" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
@@ -10908,7 +10976,11 @@
       <c r="AB99" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC99" s="4" t="inlineStr"/>
+      <c r="AC99" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="4" t="inlineStr">
@@ -11736,7 +11808,11 @@
       <c r="AB107" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC107" s="4" t="inlineStr"/>
+      <c r="AC107" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="4" t="inlineStr">
@@ -12249,7 +12325,11 @@
       <c r="AB112" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC112" s="4" t="inlineStr"/>
+      <c r="AC112" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="4" t="inlineStr">
@@ -12556,7 +12636,11 @@
       <c r="AB115" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC115" s="4" t="inlineStr"/>
+      <c r="AC115" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="4" t="inlineStr">
@@ -12657,7 +12741,11 @@
       <c r="AB116" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC116" s="4" t="inlineStr"/>
+      <c r="AC116" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="4" t="inlineStr">
@@ -13271,7 +13359,11 @@
       <c r="AB122" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC122" s="4" t="inlineStr"/>
+      <c r="AC122" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="4" t="inlineStr">
@@ -13889,7 +13981,11 @@
       <c r="AB128" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC128" s="4" t="inlineStr"/>
+      <c r="AC128" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="4" t="inlineStr">
@@ -14091,7 +14187,11 @@
       <c r="AB130" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC130" s="4" t="inlineStr"/>
+      <c r="AC130" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="4" t="inlineStr">
@@ -14192,7 +14292,11 @@
       <c r="AB131" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC131" s="4" t="inlineStr"/>
+      <c r="AC131" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="4" t="inlineStr">
@@ -16252,7 +16356,11 @@
       <c r="AB151" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC151" s="4" t="inlineStr"/>
+      <c r="AC151" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="4" t="inlineStr">
@@ -16458,7 +16566,11 @@
       <c r="AB153" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC153" s="4" t="inlineStr"/>
+      <c r="AC153" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="4" t="inlineStr">
@@ -17173,7 +17285,11 @@
       <c r="AB160" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC160" s="4" t="inlineStr"/>
+      <c r="AC160" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="4" t="inlineStr">
@@ -17686,7 +17802,11 @@
       <c r="AB165" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC165" s="4" t="inlineStr"/>
+      <c r="AC165" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="4" t="inlineStr">
@@ -17892,7 +18012,11 @@
       <c r="AB167" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC167" s="4" t="inlineStr"/>
+      <c r="AC167" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="4" t="inlineStr">
@@ -18195,7 +18319,11 @@
       <c r="AB170" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC170" s="4" t="inlineStr"/>
+      <c r="AC170" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="4" t="inlineStr">
@@ -18296,7 +18424,11 @@
       <c r="AB171" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC171" s="4" t="inlineStr"/>
+      <c r="AC171" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="4" t="inlineStr">
@@ -18607,7 +18739,11 @@
       <c r="AB174" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC174" s="4" t="inlineStr"/>
+      <c r="AC174" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="4" t="inlineStr">
@@ -19439,7 +19575,11 @@
       <c r="AB182" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC182" s="4" t="inlineStr"/>
+      <c r="AC182" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="4" t="inlineStr">
@@ -19851,7 +19991,11 @@
       <c r="AB186" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC186" s="4" t="inlineStr"/>
+      <c r="AC186" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="4" t="inlineStr">
@@ -19952,7 +20096,11 @@
       <c r="AB187" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC187" s="4" t="inlineStr"/>
+      <c r="AC187" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="4" t="inlineStr">
@@ -20158,7 +20306,11 @@
       <c r="AB189" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC189" s="4" t="inlineStr"/>
+      <c r="AC189" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="4" t="inlineStr">
@@ -20667,7 +20819,11 @@
       <c r="AB194" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC194" s="4" t="inlineStr"/>
+      <c r="AC194" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="4" t="inlineStr">
@@ -21174,7 +21330,11 @@
       <c r="AB199" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC199" s="4" t="inlineStr"/>
+      <c r="AC199" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="4" t="inlineStr">
@@ -21380,7 +21540,11 @@
       <c r="AB201" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC201" s="4" t="inlineStr"/>
+      <c r="AC201" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="4" t="inlineStr">
@@ -21687,7 +21851,11 @@
       <c r="AB204" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC204" s="4" t="inlineStr"/>
+      <c r="AC204" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" s="4" t="inlineStr">
@@ -22095,7 +22263,11 @@
       <c r="AB208" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC208" s="4" t="inlineStr"/>
+      <c r="AC208" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" s="4" t="inlineStr">
@@ -22196,7 +22368,11 @@
       <c r="AB209" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC209" s="4" t="inlineStr"/>
+      <c r="AC209" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" s="4" t="inlineStr">
@@ -22814,7 +22990,11 @@
       <c r="AB215" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC215" s="4" t="inlineStr"/>
+      <c r="AC215" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" s="4" t="inlineStr">

--- a/docs/d/80/inyear.xlsx
+++ b/docs/d/80/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>280 days remain until 30 June 2027, when these scores become final.</t>
+          <t>276 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (99 days) - 5 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 5 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (158 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 39 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 38 clubs short</t>
         </is>
       </c>
     </row>
@@ -862,13 +862,13 @@
         </is>
       </c>
       <c r="I2" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J2" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L2" s="7" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>0</v>
       </c>
       <c r="V2" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W2" s="9" t="n">
         <v>0</v>
@@ -3801,7 +3801,7 @@
         <v>0</v>
       </c>
       <c r="X30" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y30" s="9" t="n">
         <v>0</v>
@@ -9661,7 +9661,7 @@
         </is>
       </c>
       <c r="E87" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F87" s="6" t="n">
         <v>10</v>
@@ -9731,8 +9731,8 @@
       <c r="Y87" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z87" s="9" t="n">
-        <v>0</v>
+      <c r="Z87" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA87" s="10" t="n">
         <v>1</v>
@@ -10897,7 +10897,7 @@
         </is>
       </c>
       <c r="E99" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F99" s="6" t="n">
         <v>10</v>
@@ -10937,17 +10937,17 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P99" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q99" s="9" t="n">
-        <v>0</v>
+      <c r="P99" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q99" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R99" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S99" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T99" s="10" t="n">
         <v>1</v>
@@ -15809,7 +15809,7 @@
         </is>
       </c>
       <c r="P146" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q146" s="10" t="n">
         <v>2</v>
@@ -20740,7 +20740,7 @@
         </is>
       </c>
       <c r="E194" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F194" s="6" t="n">
         <v>10</v>
@@ -20783,11 +20783,11 @@
       <c r="P194" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="Q194" s="9" t="n">
-        <v>1</v>
+      <c r="Q194" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R194" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S194" s="9" t="n">
         <v>0</v>
@@ -20795,8 +20795,8 @@
       <c r="T194" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U194" s="9" t="n">
-        <v>0</v>
+      <c r="U194" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="V194" s="10" t="n">
         <v>4</v>
@@ -24053,7 +24053,7 @@
         <v>4</v>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -24152,7 +24152,7 @@
         <v>4</v>
       </c>
       <c r="D22" t="n">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -24812,13 +24812,13 @@
         <v>7</v>
       </c>
       <c r="D42" t="n">
-        <v>2.14</v>
+        <v>2.43</v>
       </c>
       <c r="E42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F42" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>

--- a/docs/d/80/inyear.xlsx
+++ b/docs/d/80/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:23 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>276 days remain until 30 June 2027, when these scores become final.</t>
+          <t>269 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 5 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 5 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 38 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 22 clubs short</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
         </is>
       </c>
       <c r="E6" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" s="6" t="n">
         <v>10</v>
@@ -1330,8 +1330,8 @@
       <c r="Y6" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z6" s="9" t="n">
-        <v>0</v>
+      <c r="Z6" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA6" s="10" t="n">
         <v>1</v>
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="E7" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" s="6" t="n">
         <v>10</v>
@@ -1435,8 +1435,8 @@
       <c r="Y7" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z7" s="9" t="n">
-        <v>0</v>
+      <c r="Z7" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA7" s="10" t="n">
         <v>1</v>
@@ -1896,13 +1896,13 @@
         </is>
       </c>
       <c r="I12" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J12" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" s="7" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
         <v>0</v>
       </c>
       <c r="V12" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W12" s="9" t="n">
         <v>0</v>
@@ -2286,7 +2286,7 @@
         </is>
       </c>
       <c r="E16" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F16" s="6" t="n">
         <v>10</v>
@@ -2356,8 +2356,8 @@
       <c r="Y16" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z16" s="9" t="n">
-        <v>0</v>
+      <c r="Z16" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA16" s="10" t="n">
         <v>1</v>
@@ -3005,7 +3005,7 @@
         </is>
       </c>
       <c r="E23" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F23" s="6" t="n">
         <v>10</v>
@@ -3045,17 +3045,17 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P23" s="9" t="n">
+      <c r="P23" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q23" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R23" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" s="10" t="n">
         <v>3</v>
-      </c>
-      <c r="Q23" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R23" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" s="10" t="n">
-        <v>2</v>
       </c>
       <c r="T23" s="10" t="n">
         <v>1</v>
@@ -3265,7 +3265,7 @@
         <v>0</v>
       </c>
       <c r="S25" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T25" s="10" t="n">
         <v>1</v>
@@ -4043,7 +4043,7 @@
         </is>
       </c>
       <c r="E33" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F33" s="6" t="n">
         <v>10</v>
@@ -4113,8 +4113,8 @@
       <c r="Y33" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z33" s="9" t="n">
-        <v>0</v>
+      <c r="Z33" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA33" s="10" t="n">
         <v>1</v>
@@ -4394,7 +4394,7 @@
         <v>0</v>
       </c>
       <c r="Q36" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R36" s="9" t="n">
         <v>0</v>
@@ -4657,7 +4657,7 @@
         </is>
       </c>
       <c r="E39" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F39" s="6" t="n">
         <v>10</v>
@@ -4671,13 +4671,13 @@
         </is>
       </c>
       <c r="I39" s="4" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="J39" s="4" t="n">
         <v>48</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
@@ -4706,8 +4706,8 @@
       <c r="R39" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="S39" s="9" t="n">
-        <v>0</v>
+      <c r="S39" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T39" s="9" t="n">
         <v>0</v>
@@ -4719,7 +4719,7 @@
         <v>4</v>
       </c>
       <c r="W39" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X39" s="10" t="n">
         <v>7</v>
@@ -4762,7 +4762,7 @@
         </is>
       </c>
       <c r="E40" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F40" s="6" t="n">
         <v>10</v>
@@ -4832,8 +4832,8 @@
       <c r="Y40" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z40" s="9" t="n">
-        <v>0</v>
+      <c r="Z40" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA40" s="10" t="n">
         <v>1</v>
@@ -6317,7 +6317,7 @@
         </is>
       </c>
       <c r="E55" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F55" s="6" t="n">
         <v>10</v>
@@ -6366,8 +6366,8 @@
       <c r="R55" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S55" s="9" t="n">
-        <v>1</v>
+      <c r="S55" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T55" s="9" t="n">
         <v>0</v>
@@ -7719,7 +7719,7 @@
         </is>
       </c>
       <c r="P68" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q68" s="9" t="n">
         <v>1</v>
@@ -9140,7 +9140,7 @@
         </is>
       </c>
       <c r="E82" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F82" s="6" t="n">
         <v>10</v>
@@ -9210,8 +9210,8 @@
       <c r="Y82" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z82" s="9" t="n">
-        <v>0</v>
+      <c r="Z82" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA82" s="10" t="n">
         <v>1</v>
@@ -9812,7 +9812,7 @@
         <v>0</v>
       </c>
       <c r="S88" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T88" s="9" t="n">
         <v>0</v>
@@ -10221,7 +10221,7 @@
         <v>2</v>
       </c>
       <c r="R92" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S92" s="9" t="n">
         <v>0</v>
@@ -10691,7 +10691,7 @@
         </is>
       </c>
       <c r="E97" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F97" s="6" t="n">
         <v>10</v>
@@ -10761,8 +10761,8 @@
       <c r="Y97" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z97" s="9" t="n">
-        <v>0</v>
+      <c r="Z97" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA97" s="10" t="n">
         <v>1</v>
@@ -10792,7 +10792,7 @@
         </is>
       </c>
       <c r="E98" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F98" s="6" t="n">
         <v>10</v>
@@ -10862,8 +10862,8 @@
       <c r="Y98" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z98" s="9" t="n">
-        <v>0</v>
+      <c r="Z98" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA98" s="10" t="n">
         <v>1</v>
@@ -11107,7 +11107,7 @@
         </is>
       </c>
       <c r="E101" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F101" s="6" t="n">
         <v>10</v>
@@ -11177,8 +11177,8 @@
       <c r="Y101" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z101" s="9" t="n">
-        <v>0</v>
+      <c r="Z101" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA101" s="10" t="n">
         <v>1</v>
@@ -11313,7 +11313,7 @@
         </is>
       </c>
       <c r="E103" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F103" s="6" t="n">
         <v>10</v>
@@ -11383,8 +11383,8 @@
       <c r="Y103" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z103" s="9" t="n">
-        <v>0</v>
+      <c r="Z103" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA103" s="10" t="n">
         <v>1</v>
@@ -11875,7 +11875,7 @@
         </is>
       </c>
       <c r="P108" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q108" s="9" t="n">
         <v>0</v>
@@ -11884,7 +11884,7 @@
         <v>0</v>
       </c>
       <c r="S108" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T108" s="9" t="n">
         <v>0</v>
@@ -12598,7 +12598,7 @@
         </is>
       </c>
       <c r="P115" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q115" s="9" t="n">
         <v>0</v>
@@ -12662,7 +12662,7 @@
         </is>
       </c>
       <c r="E116" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F116" s="6" t="n">
         <v>10</v>
@@ -12702,8 +12702,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P116" s="9" t="n">
-        <v>3</v>
+      <c r="P116" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q116" s="9" t="n">
         <v>1</v>
@@ -13148,8 +13148,8 @@
       <c r="Y120" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z120" s="9" t="n">
-        <v>0</v>
+      <c r="Z120" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA120" s="9" t="n">
         <v>0</v>
@@ -13742,7 +13742,7 @@
         <v>0</v>
       </c>
       <c r="S126" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T126" s="9" t="n">
         <v>0</v>
@@ -13952,7 +13952,7 @@
         <v>1</v>
       </c>
       <c r="S128" s="10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T128" s="10" t="n">
         <v>1</v>
@@ -14629,7 +14629,7 @@
         </is>
       </c>
       <c r="E135" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F135" s="6" t="n">
         <v>10</v>
@@ -14699,8 +14699,8 @@
       <c r="Y135" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z135" s="9" t="n">
-        <v>0</v>
+      <c r="Z135" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA135" s="10" t="n">
         <v>1</v>
@@ -15154,7 +15154,7 @@
         </is>
       </c>
       <c r="E140" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F140" s="6" t="n">
         <v>10</v>
@@ -15224,8 +15224,8 @@
       <c r="Y140" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z140" s="9" t="n">
-        <v>0</v>
+      <c r="Z140" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA140" s="10" t="n">
         <v>1</v>
@@ -15558,7 +15558,7 @@
         </is>
       </c>
       <c r="E144" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F144" s="6" t="n">
         <v>10</v>
@@ -15628,8 +15628,8 @@
       <c r="Y144" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z144" s="9" t="n">
-        <v>0</v>
+      <c r="Z144" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA144" s="10" t="n">
         <v>1</v>
@@ -15873,7 +15873,7 @@
         </is>
       </c>
       <c r="E147" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F147" s="6" t="n">
         <v>10</v>
@@ -15943,8 +15943,8 @@
       <c r="Y147" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z147" s="9" t="n">
-        <v>0</v>
+      <c r="Z147" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA147" s="10" t="n">
         <v>1</v>
@@ -16075,7 +16075,7 @@
         </is>
       </c>
       <c r="E149" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F149" s="6" t="n">
         <v>10</v>
@@ -16089,17 +16089,17 @@
         </is>
       </c>
       <c r="I149" s="4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J149" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K149" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L149" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>5</v>
+      </c>
+      <c r="L149" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M149" s="8" t="n">
@@ -16133,11 +16133,11 @@
       <c r="U149" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V149" s="9" t="n">
-        <v>3</v>
+      <c r="V149" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W149" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X149" s="10" t="n">
         <v>5</v>
@@ -16291,13 +16291,13 @@
         </is>
       </c>
       <c r="I151" s="4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J151" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K151" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L151" s="4" t="inlineStr">
         <is>
@@ -16339,7 +16339,7 @@
         <v>4</v>
       </c>
       <c r="W151" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X151" s="10" t="n">
         <v>7</v>
@@ -16501,13 +16501,13 @@
         </is>
       </c>
       <c r="I153" s="4" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J153" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K153" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L153" s="4" t="inlineStr">
         <is>
@@ -16549,7 +16549,7 @@
         <v>4</v>
       </c>
       <c r="W153" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X153" s="10" t="n">
         <v>7</v>
@@ -16642,7 +16642,7 @@
         <v>0</v>
       </c>
       <c r="S154" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T154" s="10" t="n">
         <v>1</v>
@@ -17517,7 +17517,7 @@
         </is>
       </c>
       <c r="E163" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F163" s="6" t="n">
         <v>10</v>
@@ -17531,13 +17531,13 @@
         </is>
       </c>
       <c r="I163" s="4" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J163" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K163" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L163" s="4" t="inlineStr">
         <is>
@@ -17575,11 +17575,11 @@
       <c r="U163" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="V163" s="9" t="n">
-        <v>3</v>
+      <c r="V163" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W163" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X163" s="10" t="n">
         <v>6</v>
@@ -17723,7 +17723,7 @@
         </is>
       </c>
       <c r="E165" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F165" s="6" t="n">
         <v>10</v>
@@ -17737,13 +17737,13 @@
         </is>
       </c>
       <c r="I165" s="4" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J165" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K165" s="4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L165" s="4" t="inlineStr">
         <is>
@@ -17781,11 +17781,11 @@
       <c r="U165" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V165" s="9" t="n">
-        <v>0</v>
+      <c r="V165" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W165" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X165" s="10" t="n">
         <v>7</v>
@@ -17933,7 +17933,7 @@
         </is>
       </c>
       <c r="E167" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F167" s="6" t="n">
         <v>10</v>
@@ -17947,13 +17947,13 @@
         </is>
       </c>
       <c r="I167" s="4" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="J167" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K167" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L167" s="4" t="inlineStr">
         <is>
@@ -17991,11 +17991,11 @@
       <c r="U167" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V167" s="9" t="n">
-        <v>1</v>
+      <c r="V167" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W167" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X167" s="10" t="n">
         <v>6</v>
@@ -18389,7 +18389,7 @@
         <v>2</v>
       </c>
       <c r="Q171" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R171" s="9" t="n">
         <v>0</v>
@@ -18450,7 +18450,7 @@
         </is>
       </c>
       <c r="E172" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F172" s="6" t="n">
         <v>10</v>
@@ -18491,22 +18491,22 @@
         </is>
       </c>
       <c r="P172" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q172" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R172" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S172" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T172" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U172" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T172" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U172" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="V172" s="9" t="n">
         <v>0</v>
@@ -20584,7 +20584,7 @@
         <v>1</v>
       </c>
       <c r="S192" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T192" s="10" t="n">
         <v>1</v>
@@ -21045,7 +21045,7 @@
         </is>
       </c>
       <c r="E197" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F197" s="6" t="n">
         <v>10</v>
@@ -21059,13 +21059,13 @@
         </is>
       </c>
       <c r="I197" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J197" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K197" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L197" s="7" t="inlineStr">
         <is>
@@ -21104,7 +21104,7 @@
         <v>0</v>
       </c>
       <c r="V197" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W197" s="9" t="n">
         <v>0</v>
@@ -21115,8 +21115,8 @@
       <c r="Y197" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z197" s="9" t="n">
-        <v>0</v>
+      <c r="Z197" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA197" s="10" t="n">
         <v>1</v>
@@ -21822,7 +21822,7 @@
         <v>0</v>
       </c>
       <c r="S204" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T204" s="10" t="n">
         <v>1</v>
@@ -22139,7 +22139,7 @@
         <v>1</v>
       </c>
       <c r="U207" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V207" s="9" t="n">
         <v>2</v>
@@ -22184,7 +22184,7 @@
         </is>
       </c>
       <c r="E208" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F208" s="6" t="n">
         <v>10</v>
@@ -22233,8 +22233,8 @@
       <c r="R208" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S208" s="9" t="n">
-        <v>1</v>
+      <c r="S208" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T208" s="10" t="n">
         <v>1</v>
@@ -22289,7 +22289,7 @@
         </is>
       </c>
       <c r="E209" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F209" s="6" t="n">
         <v>10</v>
@@ -22330,10 +22330,10 @@
         </is>
       </c>
       <c r="P209" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q209" s="10" t="n">
         <v>2</v>
-      </c>
-      <c r="Q209" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="R209" s="9" t="n">
         <v>0</v>
@@ -22540,7 +22540,7 @@
         </is>
       </c>
       <c r="P211" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q211" s="9" t="n">
         <v>1</v>
@@ -23525,7 +23525,7 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
@@ -23591,7 +23591,7 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -23657,13 +23657,13 @@
         <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -23723,7 +23723,7 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E9" t="n">
         <v>1</v>
@@ -23756,13 +23756,13 @@
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -23789,7 +23789,7 @@
         <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -23855,7 +23855,7 @@
         <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -24020,7 +24020,7 @@
         <v>5</v>
       </c>
       <c r="D18" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -24119,7 +24119,7 @@
         <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -24152,7 +24152,7 @@
         <v>4</v>
       </c>
       <c r="D22" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -24185,7 +24185,7 @@
         <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="E23" t="n">
         <v>1</v>
@@ -24251,13 +24251,13 @@
         <v>5</v>
       </c>
       <c r="D25" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -24383,7 +24383,7 @@
         <v>5</v>
       </c>
       <c r="D29" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -24449,7 +24449,7 @@
         <v>4</v>
       </c>
       <c r="D31" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
@@ -24482,7 +24482,7 @@
         <v>4</v>
       </c>
       <c r="D32" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
@@ -24515,7 +24515,7 @@
         <v>5</v>
       </c>
       <c r="D33" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
@@ -24530,7 +24530,7 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="34">
@@ -24614,7 +24614,7 @@
         <v>5</v>
       </c>
       <c r="D36" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
@@ -24647,7 +24647,7 @@
         <v>5</v>
       </c>
       <c r="D37" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>
@@ -24812,7 +24812,7 @@
         <v>7</v>
       </c>
       <c r="D42" t="n">
-        <v>2.43</v>
+        <v>2.57</v>
       </c>
       <c r="E42" t="n">
         <v>2</v>
@@ -24878,13 +24878,13 @@
         <v>6</v>
       </c>
       <c r="D44" t="n">
-        <v>3</v>
+        <v>3.33</v>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F44" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>

--- a/docs/d/80/inyear.xlsx
+++ b/docs/d/80/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:23 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>269 days remain until 30 June 2027, when these scores become final.</t>
+          <t>262 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 5 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 5 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 22 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 21 clubs short</t>
         </is>
       </c>
     </row>
@@ -862,13 +862,13 @@
         </is>
       </c>
       <c r="I2" s="4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J2" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="L2" s="7" t="inlineStr">
         <is>
@@ -949,7 +949,7 @@
         </is>
       </c>
       <c r="E3" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3" s="6" t="n">
         <v>10</v>
@@ -963,17 +963,17 @@
         </is>
       </c>
       <c r="I3" s="4" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="J3" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L3" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L3" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M3" s="8" t="n">
@@ -1001,14 +1001,14 @@
       <c r="S3" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T3" s="9" t="n">
-        <v>0</v>
+      <c r="T3" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U3" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V3" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W3" s="9" t="n">
         <v>0</v>
@@ -1068,13 +1068,13 @@
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>106</v>
+        <v>85</v>
       </c>
       <c r="J4" s="4" t="n">
         <v>95</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>11</v>
+        <v>-10</v>
       </c>
       <c r="L4" s="4" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>4</v>
       </c>
       <c r="Q4" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R4" s="9" t="n">
         <v>0</v>
@@ -1173,13 +1173,13 @@
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L5" s="7" t="inlineStr">
         <is>
@@ -1274,17 +1274,17 @@
         </is>
       </c>
       <c r="I6" s="4" t="n">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="J6" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-15</v>
+      </c>
+      <c r="L6" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M6" s="8" t="n">
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="E7" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7" s="6" t="n">
         <v>10</v>
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J7" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="L7" s="7" t="inlineStr">
         <is>
@@ -1423,11 +1423,11 @@
       <c r="U7" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V7" s="9" t="n">
-        <v>2</v>
+      <c r="V7" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W7" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X7" s="10" t="n">
         <v>7</v>
@@ -1480,13 +1480,13 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
         <v>1</v>
       </c>
       <c r="V8" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W8" s="9" t="n">
         <v>0</v>
@@ -1585,17 +1585,17 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="J9" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L9" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L9" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M9" s="8" t="n">
@@ -1690,13 +1690,13 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L10" s="7" t="inlineStr">
         <is>
@@ -1735,7 +1735,7 @@
         <v>0</v>
       </c>
       <c r="V10" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W10" s="9" t="n">
         <v>0</v>
@@ -1791,13 +1791,13 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
@@ -1896,13 +1896,13 @@
         </is>
       </c>
       <c r="I12" s="4" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="J12" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L12" s="7" t="inlineStr">
         <is>
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="I13" s="4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J13" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L13" s="7" t="inlineStr">
         <is>
@@ -2098,13 +2098,13 @@
         </is>
       </c>
       <c r="I14" s="4" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="J14" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L14" s="7" t="inlineStr">
         <is>
@@ -2199,13 +2199,13 @@
         </is>
       </c>
       <c r="I15" s="4" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="J15" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="L15" s="7" t="inlineStr">
         <is>
@@ -2300,17 +2300,17 @@
         </is>
       </c>
       <c r="I16" s="4" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="J16" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-10</v>
+      </c>
+      <c r="L16" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M16" s="8" t="n">
@@ -2401,13 +2401,13 @@
         </is>
       </c>
       <c r="I17" s="4" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J17" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L17" s="7" t="inlineStr">
         <is>
@@ -2502,13 +2502,13 @@
         </is>
       </c>
       <c r="I18" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J18" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
@@ -2547,7 +2547,7 @@
         <v>0</v>
       </c>
       <c r="V18" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W18" s="9" t="n">
         <v>0</v>
@@ -2603,13 +2603,13 @@
         </is>
       </c>
       <c r="I19" s="4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J19" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L19" s="7" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         </is>
       </c>
       <c r="P19" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q19" s="9" t="n">
         <v>0</v>
@@ -2639,7 +2639,7 @@
         <v>0</v>
       </c>
       <c r="S19" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T19" s="9" t="n">
         <v>0</v>
@@ -2648,7 +2648,7 @@
         <v>0</v>
       </c>
       <c r="V19" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W19" s="9" t="n">
         <v>0</v>
@@ -2704,13 +2704,13 @@
         </is>
       </c>
       <c r="I20" s="4" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J20" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L20" s="4" t="inlineStr">
         <is>
@@ -2749,7 +2749,7 @@
         <v>1</v>
       </c>
       <c r="V20" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W20" s="9" t="n">
         <v>0</v>
@@ -2809,17 +2809,17 @@
         </is>
       </c>
       <c r="I21" s="4" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J21" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L21" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L21" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M21" s="8" t="n">
@@ -2900,7 +2900,7 @@
         </is>
       </c>
       <c r="E22" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F22" s="6" t="n">
         <v>10</v>
@@ -2914,13 +2914,13 @@
         </is>
       </c>
       <c r="I22" s="4" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J22" s="4" t="n">
         <v>43</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="L22" s="4" t="inlineStr">
         <is>
@@ -2952,14 +2952,14 @@
       <c r="S22" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="T22" s="9" t="n">
-        <v>0</v>
+      <c r="T22" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U22" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V22" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W22" s="9" t="n">
         <v>0</v>
@@ -3005,7 +3005,7 @@
         </is>
       </c>
       <c r="E23" s="5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F23" s="6" t="n">
         <v>10</v>
@@ -3019,13 +3019,13 @@
         </is>
       </c>
       <c r="I23" s="4" t="n">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="J23" s="4" t="n">
         <v>58</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="L23" s="4" t="inlineStr">
         <is>
@@ -3063,11 +3063,11 @@
       <c r="U23" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="V23" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="W23" s="9" t="n">
-        <v>0</v>
+      <c r="V23" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W23" s="10" t="n">
+        <v>19</v>
       </c>
       <c r="X23" s="10" t="n">
         <v>7</v>
@@ -3124,13 +3124,13 @@
         </is>
       </c>
       <c r="I24" s="4" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="J24" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="L24" s="4" t="inlineStr">
         <is>
@@ -3169,7 +3169,7 @@
         <v>0</v>
       </c>
       <c r="V24" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W24" s="9" t="n">
         <v>0</v>
@@ -3229,17 +3229,17 @@
         </is>
       </c>
       <c r="I25" s="4" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J25" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L25" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L25" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M25" s="8" t="n">
@@ -3256,7 +3256,7 @@
         </is>
       </c>
       <c r="P25" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q25" s="9" t="n">
         <v>1</v>
@@ -3334,13 +3334,13 @@
         </is>
       </c>
       <c r="I26" s="4" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J26" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L26" s="7" t="inlineStr">
         <is>
@@ -3435,13 +3435,13 @@
         </is>
       </c>
       <c r="I27" s="4" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="J27" s="4" t="n">
         <v>57</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L27" s="4" t="inlineStr">
         <is>
@@ -3526,7 +3526,7 @@
         </is>
       </c>
       <c r="E28" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F28" s="6" t="n">
         <v>10</v>
@@ -3540,13 +3540,13 @@
         </is>
       </c>
       <c r="I28" s="4" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="J28" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>2</v>
+        <v>-7</v>
       </c>
       <c r="L28" s="4" t="inlineStr">
         <is>
@@ -3584,8 +3584,8 @@
       <c r="U28" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V28" s="9" t="n">
-        <v>2</v>
+      <c r="V28" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W28" s="9" t="n">
         <v>0</v>
@@ -3645,17 +3645,17 @@
         </is>
       </c>
       <c r="I29" s="4" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="J29" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L29" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M29" s="8" t="n">
@@ -3690,7 +3690,7 @@
         <v>0</v>
       </c>
       <c r="V29" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W29" s="9" t="n">
         <v>0</v>
@@ -3750,13 +3750,13 @@
         </is>
       </c>
       <c r="I30" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J30" s="4" t="n">
         <v>7</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L30" s="7" t="inlineStr">
         <is>
@@ -3851,17 +3851,17 @@
         </is>
       </c>
       <c r="I31" s="4" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="J31" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L31" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M31" s="8" t="n">
@@ -3942,7 +3942,7 @@
         </is>
       </c>
       <c r="E32" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F32" s="6" t="n">
         <v>10</v>
@@ -3956,13 +3956,13 @@
         </is>
       </c>
       <c r="I32" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J32" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L32" s="7" t="inlineStr">
         <is>
@@ -3994,8 +3994,8 @@
       <c r="S32" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T32" s="9" t="n">
-        <v>0</v>
+      <c r="T32" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U32" s="9" t="n">
         <v>0</v>
@@ -4057,13 +4057,13 @@
         </is>
       </c>
       <c r="I33" s="4" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J33" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L33" s="4" t="inlineStr">
         <is>
@@ -4102,7 +4102,7 @@
         <v>0</v>
       </c>
       <c r="V33" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W33" s="9" t="n">
         <v>0</v>
@@ -4162,13 +4162,13 @@
         </is>
       </c>
       <c r="I34" s="4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J34" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L34" s="7" t="inlineStr">
         <is>
@@ -4249,7 +4249,7 @@
         </is>
       </c>
       <c r="E35" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F35" s="6" t="n">
         <v>10</v>
@@ -4263,13 +4263,13 @@
         </is>
       </c>
       <c r="I35" s="4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J35" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L35" s="7" t="inlineStr">
         <is>
@@ -4307,11 +4307,11 @@
       <c r="U35" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V35" s="9" t="n">
-        <v>0</v>
+      <c r="V35" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W35" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X35" s="9" t="n">
         <v>0</v>
@@ -4465,13 +4465,13 @@
         </is>
       </c>
       <c r="I37" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J37" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L37" s="7" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         </is>
       </c>
       <c r="E38" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F38" s="6" t="n">
         <v>10</v>
@@ -4566,13 +4566,13 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="J38" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="L38" s="4" t="inlineStr">
         <is>
@@ -4610,11 +4610,11 @@
       <c r="U38" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V38" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W38" s="9" t="n">
-        <v>0</v>
+      <c r="V38" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W38" s="10" t="n">
+        <v>27</v>
       </c>
       <c r="X38" s="10" t="n">
         <v>6</v>
@@ -4671,13 +4671,13 @@
         </is>
       </c>
       <c r="I39" s="4" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="J39" s="4" t="n">
         <v>48</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>7</v>
+        <v>-8</v>
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
@@ -4776,17 +4776,17 @@
         </is>
       </c>
       <c r="I40" s="4" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J40" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L40" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L40" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M40" s="8" t="n">
@@ -4821,7 +4821,7 @@
         <v>0</v>
       </c>
       <c r="V40" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W40" s="9" t="n">
         <v>0</v>
@@ -4877,13 +4877,13 @@
         </is>
       </c>
       <c r="I41" s="4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J41" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K41" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L41" s="7" t="inlineStr">
         <is>
@@ -4978,13 +4978,13 @@
         </is>
       </c>
       <c r="I42" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J42" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L42" s="4" t="inlineStr">
         <is>
@@ -5023,7 +5023,7 @@
         <v>0</v>
       </c>
       <c r="V42" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W42" s="9" t="n">
         <v>0</v>
@@ -5069,7 +5069,7 @@
         </is>
       </c>
       <c r="E43" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F43" s="6" t="n">
         <v>10</v>
@@ -5083,17 +5083,17 @@
         </is>
       </c>
       <c r="I43" s="4" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="J43" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L43" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L43" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M43" s="8" t="n">
@@ -5127,8 +5127,8 @@
       <c r="U43" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V43" s="9" t="n">
-        <v>3</v>
+      <c r="V43" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W43" s="9" t="n">
         <v>0</v>
@@ -5188,17 +5188,17 @@
         </is>
       </c>
       <c r="I44" s="4" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="J44" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L44" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L44" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M44" s="8" t="n">
@@ -5233,7 +5233,7 @@
         <v>0</v>
       </c>
       <c r="V44" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W44" s="9" t="n">
         <v>0</v>
@@ -5394,13 +5394,13 @@
         </is>
       </c>
       <c r="I46" s="4" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J46" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L46" s="4" t="inlineStr">
         <is>
@@ -5499,13 +5499,13 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="J47" s="4" t="n">
         <v>82</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="L47" s="4" t="inlineStr">
         <is>
@@ -5750,7 +5750,7 @@
         <v>0</v>
       </c>
       <c r="V49" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W49" s="9" t="n">
         <v>0</v>
@@ -5806,13 +5806,13 @@
         </is>
       </c>
       <c r="I50" s="4" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J50" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L50" s="4" t="inlineStr">
         <is>
@@ -5911,17 +5911,17 @@
         </is>
       </c>
       <c r="I51" s="4" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J51" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K51" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L51" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L51" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M51" s="8" t="n">
@@ -6016,17 +6016,17 @@
         </is>
       </c>
       <c r="I52" s="4" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="J52" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L52" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L52" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M52" s="8" t="n">
@@ -6121,17 +6121,17 @@
         </is>
       </c>
       <c r="I53" s="4" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J53" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K53" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L53" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L53" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M53" s="8" t="n">
@@ -6212,7 +6212,7 @@
         </is>
       </c>
       <c r="E54" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F54" s="6" t="n">
         <v>10</v>
@@ -6226,13 +6226,13 @@
         </is>
       </c>
       <c r="I54" s="4" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="J54" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L54" s="4" t="inlineStr">
         <is>
@@ -6252,8 +6252,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P54" s="9" t="n">
-        <v>2</v>
+      <c r="P54" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q54" s="9" t="n">
         <v>0</v>
@@ -6273,8 +6273,8 @@
       <c r="V54" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W54" s="9" t="n">
-        <v>3</v>
+      <c r="W54" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X54" s="10" t="n">
         <v>7</v>
@@ -6331,17 +6331,17 @@
         </is>
       </c>
       <c r="I55" s="4" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J55" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K55" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L55" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L55" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M55" s="8" t="n">
@@ -6436,17 +6436,17 @@
         </is>
       </c>
       <c r="I56" s="4" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J56" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K56" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L56" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L56" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M56" s="8" t="n">
@@ -6541,17 +6541,17 @@
         </is>
       </c>
       <c r="I57" s="4" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="J57" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L57" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-13</v>
+      </c>
+      <c r="L57" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M57" s="8" t="n">
@@ -6646,17 +6646,17 @@
         </is>
       </c>
       <c r="I58" s="4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J58" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K58" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L58" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-1</v>
+      </c>
+      <c r="L58" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M58" s="8" t="n">
@@ -6751,17 +6751,17 @@
         </is>
       </c>
       <c r="I59" s="4" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J59" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K59" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L59" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L59" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M59" s="8" t="n">
@@ -6961,13 +6961,13 @@
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J61" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L61" s="7" t="inlineStr">
         <is>
@@ -7171,13 +7171,13 @@
         </is>
       </c>
       <c r="I63" s="4" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="J63" s="4" t="n">
         <v>39</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="L63" s="4" t="inlineStr">
         <is>
@@ -7276,13 +7276,13 @@
         </is>
       </c>
       <c r="I64" s="4" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J64" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>4</v>
+        <v>-2</v>
       </c>
       <c r="L64" s="7" t="inlineStr">
         <is>
@@ -7377,13 +7377,13 @@
         </is>
       </c>
       <c r="I65" s="4" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J65" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K65" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L65" s="4" t="inlineStr">
         <is>
@@ -7482,13 +7482,13 @@
         </is>
       </c>
       <c r="I66" s="4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J66" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K66" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L66" s="7" t="inlineStr">
         <is>
@@ -7587,17 +7587,17 @@
         </is>
       </c>
       <c r="I67" s="4" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="J67" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L67" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L67" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M67" s="8" t="n">
@@ -7692,17 +7692,17 @@
         </is>
       </c>
       <c r="I68" s="4" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="J68" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K68" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L68" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L68" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M68" s="8" t="n">
@@ -7797,13 +7797,13 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J69" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K69" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L69" s="4" t="inlineStr">
         <is>
@@ -7898,17 +7898,17 @@
         </is>
       </c>
       <c r="I70" s="4" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J70" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K70" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L70" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-1</v>
+      </c>
+      <c r="L70" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M70" s="8" t="n">
@@ -7943,7 +7943,7 @@
         <v>0</v>
       </c>
       <c r="V70" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W70" s="9" t="n">
         <v>0</v>
@@ -8003,17 +8003,17 @@
         </is>
       </c>
       <c r="I71" s="4" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J71" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K71" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L71" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L71" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M71" s="8" t="n">
@@ -8108,13 +8108,13 @@
         </is>
       </c>
       <c r="I72" s="4" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="J72" s="4" t="n">
         <v>35</v>
       </c>
       <c r="K72" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L72" s="4" t="inlineStr">
         <is>
@@ -8156,7 +8156,7 @@
         <v>4</v>
       </c>
       <c r="W72" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X72" s="10" t="n">
         <v>7</v>
@@ -8213,17 +8213,17 @@
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J73" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L73" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L73" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M73" s="8" t="n">
@@ -8318,17 +8318,17 @@
         </is>
       </c>
       <c r="I74" s="4" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J74" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K74" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L74" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L74" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M74" s="8" t="n">
@@ -8528,13 +8528,13 @@
         </is>
       </c>
       <c r="I76" s="4" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="J76" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K76" s="4" t="n">
-        <v>4</v>
+        <v>-4</v>
       </c>
       <c r="L76" s="4" t="inlineStr">
         <is>
@@ -8619,7 +8619,7 @@
         </is>
       </c>
       <c r="E77" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F77" s="6" t="n">
         <v>10</v>
@@ -8633,13 +8633,13 @@
         </is>
       </c>
       <c r="I77" s="4" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="J77" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K77" s="4" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="L77" s="4" t="inlineStr">
         <is>
@@ -8662,8 +8662,8 @@
       <c r="P77" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="Q77" s="9" t="n">
-        <v>0</v>
+      <c r="Q77" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R77" s="9" t="n">
         <v>0</v>
@@ -8681,7 +8681,7 @@
         <v>4</v>
       </c>
       <c r="W77" s="10" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="X77" s="10" t="n">
         <v>7</v>
@@ -8738,17 +8738,17 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="J78" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L78" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-11</v>
+      </c>
+      <c r="L78" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M78" s="8" t="n">
@@ -8783,7 +8783,7 @@
         <v>0</v>
       </c>
       <c r="V78" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W78" s="9" t="n">
         <v>0</v>
@@ -8843,13 +8843,13 @@
         </is>
       </c>
       <c r="I79" s="4" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="J79" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K79" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L79" s="4" t="inlineStr">
         <is>
@@ -8948,17 +8948,17 @@
         </is>
       </c>
       <c r="I80" s="4" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="J80" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K80" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L80" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L80" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M80" s="8" t="n">
@@ -9053,13 +9053,13 @@
         </is>
       </c>
       <c r="I81" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J81" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K81" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L81" s="7" t="inlineStr">
         <is>
@@ -9154,17 +9154,17 @@
         </is>
       </c>
       <c r="I82" s="4" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J82" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K82" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L82" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L82" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M82" s="8" t="n">
@@ -9199,7 +9199,7 @@
         <v>0</v>
       </c>
       <c r="V82" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W82" s="9" t="n">
         <v>0</v>
@@ -9259,17 +9259,17 @@
         </is>
       </c>
       <c r="I83" s="4" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J83" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K83" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L83" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L83" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M83" s="8" t="n">
@@ -9286,7 +9286,7 @@
         </is>
       </c>
       <c r="P83" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q83" s="9" t="n">
         <v>0</v>
@@ -9304,7 +9304,7 @@
         <v>0</v>
       </c>
       <c r="V83" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W83" s="9" t="n">
         <v>0</v>
@@ -9364,13 +9364,13 @@
         </is>
       </c>
       <c r="I84" s="4" t="n">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="J84" s="4" t="n">
         <v>53</v>
       </c>
       <c r="K84" s="4" t="n">
-        <v>5</v>
+        <v>-5</v>
       </c>
       <c r="L84" s="4" t="inlineStr">
         <is>
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J85" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K85" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L85" s="7" t="inlineStr">
         <is>
@@ -9570,17 +9570,17 @@
         </is>
       </c>
       <c r="I86" s="4" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="J86" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K86" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L86" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-13</v>
+      </c>
+      <c r="L86" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M86" s="8" t="n">
@@ -9675,13 +9675,13 @@
         </is>
       </c>
       <c r="I87" s="4" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J87" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K87" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L87" s="7" t="inlineStr">
         <is>
@@ -9762,7 +9762,7 @@
         </is>
       </c>
       <c r="E88" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F88" s="6" t="n">
         <v>10</v>
@@ -9776,13 +9776,13 @@
         </is>
       </c>
       <c r="I88" s="4" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="J88" s="4" t="n">
         <v>37</v>
       </c>
       <c r="K88" s="4" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="L88" s="4" t="inlineStr">
         <is>
@@ -9820,8 +9820,8 @@
       <c r="U88" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V88" s="9" t="n">
-        <v>2</v>
+      <c r="V88" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W88" s="9" t="n">
         <v>0</v>
@@ -9867,7 +9867,7 @@
         </is>
       </c>
       <c r="E89" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F89" s="6" t="n">
         <v>10</v>
@@ -9925,11 +9925,11 @@
       <c r="U89" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V89" s="9" t="n">
-        <v>2</v>
+      <c r="V89" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W89" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X89" s="10" t="n">
         <v>5</v>
@@ -9982,17 +9982,17 @@
         </is>
       </c>
       <c r="I90" s="4" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J90" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K90" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L90" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L90" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M90" s="8" t="n">
@@ -10012,7 +10012,7 @@
         <v>0</v>
       </c>
       <c r="Q90" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R90" s="9" t="n">
         <v>0</v>
@@ -10087,13 +10087,13 @@
         </is>
       </c>
       <c r="I91" s="4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J91" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K91" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L91" s="7" t="inlineStr">
         <is>
@@ -10174,7 +10174,7 @@
         </is>
       </c>
       <c r="E92" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F92" s="6" t="n">
         <v>10</v>
@@ -10188,13 +10188,13 @@
         </is>
       </c>
       <c r="I92" s="4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J92" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K92" s="4" t="n">
-        <v>3</v>
+        <v>-2</v>
       </c>
       <c r="L92" s="7" t="inlineStr">
         <is>
@@ -10226,8 +10226,8 @@
       <c r="S92" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T92" s="9" t="n">
-        <v>0</v>
+      <c r="T92" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U92" s="9" t="n">
         <v>0</v>
@@ -10289,13 +10289,13 @@
         </is>
       </c>
       <c r="I93" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J93" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K93" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L93" s="7" t="inlineStr">
         <is>
@@ -10435,7 +10435,7 @@
         <v>0</v>
       </c>
       <c r="V94" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W94" s="9" t="n">
         <v>0</v>
@@ -10481,7 +10481,7 @@
         </is>
       </c>
       <c r="E95" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F95" s="6" t="n">
         <v>10</v>
@@ -10495,13 +10495,13 @@
         </is>
       </c>
       <c r="I95" s="4" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J95" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K95" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L95" s="4" t="inlineStr">
         <is>
@@ -10522,7 +10522,7 @@
         </is>
       </c>
       <c r="P95" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q95" s="9" t="n">
         <v>0</v>
@@ -10539,11 +10539,11 @@
       <c r="U95" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V95" s="9" t="n">
-        <v>3</v>
+      <c r="V95" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W95" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X95" s="10" t="n">
         <v>4</v>
@@ -10600,17 +10600,17 @@
         </is>
       </c>
       <c r="I96" s="4" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="J96" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K96" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L96" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L96" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M96" s="8" t="n">
@@ -10705,13 +10705,13 @@
         </is>
       </c>
       <c r="I97" s="4" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="J97" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K97" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L97" s="7" t="inlineStr">
         <is>
@@ -10750,7 +10750,7 @@
         <v>0</v>
       </c>
       <c r="V97" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W97" s="9" t="n">
         <v>0</v>
@@ -10806,13 +10806,13 @@
         </is>
       </c>
       <c r="I98" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J98" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K98" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L98" s="7" t="inlineStr">
         <is>
@@ -10911,13 +10911,13 @@
         </is>
       </c>
       <c r="I99" s="4" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="J99" s="4" t="n">
         <v>55</v>
       </c>
       <c r="K99" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L99" s="4" t="inlineStr">
         <is>
@@ -10938,7 +10938,7 @@
         </is>
       </c>
       <c r="P99" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q99" s="10" t="n">
         <v>2</v>
@@ -11016,17 +11016,17 @@
         </is>
       </c>
       <c r="I100" s="4" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J100" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K100" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L100" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L100" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M100" s="8" t="n">
@@ -11107,7 +11107,7 @@
         </is>
       </c>
       <c r="E101" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F101" s="6" t="n">
         <v>10</v>
@@ -11121,17 +11121,17 @@
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="J101" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K101" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L101" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L101" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M101" s="8" t="n">
@@ -11165,11 +11165,11 @@
       <c r="U101" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V101" s="9" t="n">
-        <v>0</v>
+      <c r="V101" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W101" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X101" s="10" t="n">
         <v>6</v>
@@ -11327,13 +11327,13 @@
         </is>
       </c>
       <c r="I103" s="4" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J103" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K103" s="4" t="n">
-        <v>2</v>
+        <v>-4</v>
       </c>
       <c r="L103" s="7" t="inlineStr">
         <is>
@@ -11537,17 +11537,17 @@
         </is>
       </c>
       <c r="I105" s="4" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J105" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K105" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L105" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L105" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M105" s="8" t="n">
@@ -11743,13 +11743,13 @@
         </is>
       </c>
       <c r="I107" s="4" t="n">
-        <v>127</v>
+        <v>97</v>
       </c>
       <c r="J107" s="4" t="n">
         <v>109</v>
       </c>
       <c r="K107" s="4" t="n">
-        <v>18</v>
+        <v>-12</v>
       </c>
       <c r="L107" s="4" t="inlineStr">
         <is>
@@ -11791,7 +11791,7 @@
         <v>4</v>
       </c>
       <c r="W107" s="10" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="X107" s="10" t="n">
         <v>4</v>
@@ -11848,17 +11848,17 @@
         </is>
       </c>
       <c r="I108" s="4" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="J108" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K108" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L108" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L108" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M108" s="8" t="n">
@@ -11893,7 +11893,7 @@
         <v>0</v>
       </c>
       <c r="V108" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W108" s="9" t="n">
         <v>0</v>
@@ -11953,13 +11953,13 @@
         </is>
       </c>
       <c r="I109" s="4" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J109" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K109" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L109" s="7" t="inlineStr">
         <is>
@@ -12054,13 +12054,13 @@
         </is>
       </c>
       <c r="I110" s="4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J110" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K110" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L110" s="4" t="inlineStr">
         <is>
@@ -12155,17 +12155,17 @@
         </is>
       </c>
       <c r="I111" s="4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J111" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K111" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L111" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-9</v>
+      </c>
+      <c r="L111" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M111" s="8" t="n">
@@ -12260,17 +12260,17 @@
         </is>
       </c>
       <c r="I112" s="4" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="J112" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K112" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L112" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L112" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M112" s="8" t="n">
@@ -12365,13 +12365,13 @@
         </is>
       </c>
       <c r="I113" s="4" t="n">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="J113" s="4" t="n">
         <v>37</v>
       </c>
       <c r="K113" s="4" t="n">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="L113" s="4" t="inlineStr">
         <is>
@@ -12410,7 +12410,7 @@
         <v>1</v>
       </c>
       <c r="V113" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W113" s="9" t="n">
         <v>0</v>
@@ -12571,17 +12571,17 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="J115" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K115" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L115" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L115" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M115" s="8" t="n">
@@ -12601,7 +12601,7 @@
         <v>1</v>
       </c>
       <c r="Q115" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R115" s="9" t="n">
         <v>0</v>
@@ -12662,7 +12662,7 @@
         </is>
       </c>
       <c r="E116" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F116" s="6" t="n">
         <v>10</v>
@@ -12676,13 +12676,13 @@
         </is>
       </c>
       <c r="I116" s="4" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="J116" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K116" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L116" s="4" t="inlineStr">
         <is>
@@ -12703,7 +12703,7 @@
         </is>
       </c>
       <c r="P116" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q116" s="9" t="n">
         <v>1</v>
@@ -12723,8 +12723,8 @@
       <c r="V116" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W116" s="9" t="n">
-        <v>2</v>
+      <c r="W116" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="X116" s="10" t="n">
         <v>7</v>
@@ -12886,13 +12886,13 @@
         </is>
       </c>
       <c r="I118" s="4" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J118" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K118" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L118" s="7" t="inlineStr">
         <is>
@@ -12931,7 +12931,7 @@
         <v>0</v>
       </c>
       <c r="V118" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W118" s="9" t="n">
         <v>0</v>
@@ -12987,17 +12987,17 @@
         </is>
       </c>
       <c r="I119" s="4" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="J119" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K119" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L119" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L119" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M119" s="8" t="n">
@@ -13092,13 +13092,13 @@
         </is>
       </c>
       <c r="I120" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J120" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K120" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L120" s="7" t="inlineStr">
         <is>
@@ -13137,7 +13137,7 @@
         <v>0</v>
       </c>
       <c r="V120" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W120" s="9" t="n">
         <v>0</v>
@@ -13193,13 +13193,13 @@
         </is>
       </c>
       <c r="I121" s="4" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="J121" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K121" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L121" s="7" t="inlineStr">
         <is>
@@ -13280,7 +13280,7 @@
         </is>
       </c>
       <c r="E122" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F122" s="6" t="n">
         <v>10</v>
@@ -13294,13 +13294,13 @@
         </is>
       </c>
       <c r="I122" s="4" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="J122" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K122" s="4" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="L122" s="4" t="inlineStr">
         <is>
@@ -13335,8 +13335,8 @@
       <c r="T122" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U122" s="9" t="n">
-        <v>0</v>
+      <c r="U122" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V122" s="10" t="n">
         <v>4</v>
@@ -13399,13 +13399,13 @@
         </is>
       </c>
       <c r="I123" s="4" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J123" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K123" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L123" s="4" t="inlineStr">
         <is>
@@ -13444,7 +13444,7 @@
         <v>0</v>
       </c>
       <c r="V123" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W123" s="9" t="n">
         <v>0</v>
@@ -13504,13 +13504,13 @@
         </is>
       </c>
       <c r="I124" s="4" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="J124" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K124" s="4" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="L124" s="7" t="inlineStr">
         <is>
@@ -13591,7 +13591,7 @@
         </is>
       </c>
       <c r="E125" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F125" s="6" t="n">
         <v>10</v>
@@ -13605,13 +13605,13 @@
         </is>
       </c>
       <c r="I125" s="4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J125" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K125" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L125" s="7" t="inlineStr">
         <is>
@@ -13649,11 +13649,11 @@
       <c r="U125" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V125" s="9" t="n">
-        <v>3</v>
+      <c r="V125" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W125" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X125" s="10" t="n">
         <v>7</v>
@@ -13706,13 +13706,13 @@
         </is>
       </c>
       <c r="I126" s="4" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J126" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K126" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L126" s="4" t="inlineStr">
         <is>
@@ -13811,13 +13811,13 @@
         </is>
       </c>
       <c r="I127" s="4" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J127" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K127" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L127" s="4" t="inlineStr">
         <is>
@@ -13838,7 +13838,7 @@
         </is>
       </c>
       <c r="P127" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q127" s="9" t="n">
         <v>0</v>
@@ -13916,13 +13916,13 @@
         </is>
       </c>
       <c r="I128" s="4" t="n">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="J128" s="4" t="n">
         <v>61</v>
       </c>
       <c r="K128" s="4" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="L128" s="4" t="inlineStr">
         <is>
@@ -13964,7 +13964,7 @@
         <v>4</v>
       </c>
       <c r="W128" s="10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X128" s="10" t="n">
         <v>6</v>
@@ -14021,13 +14021,13 @@
         </is>
       </c>
       <c r="I129" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J129" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K129" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L129" s="7" t="inlineStr">
         <is>
@@ -14066,7 +14066,7 @@
         <v>0</v>
       </c>
       <c r="V129" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W129" s="9" t="n">
         <v>0</v>
@@ -14122,13 +14122,13 @@
         </is>
       </c>
       <c r="I130" s="4" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J130" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K130" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L130" s="4" t="inlineStr">
         <is>
@@ -14227,17 +14227,17 @@
         </is>
       </c>
       <c r="I131" s="4" t="n">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="J131" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K131" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L131" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-13</v>
+      </c>
+      <c r="L131" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M131" s="8" t="n">
@@ -14332,17 +14332,17 @@
         </is>
       </c>
       <c r="I132" s="4" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="J132" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K132" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L132" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-15</v>
+      </c>
+      <c r="L132" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M132" s="8" t="n">
@@ -14433,17 +14433,17 @@
         </is>
       </c>
       <c r="I133" s="4" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J133" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K133" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L133" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L133" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M133" s="8" t="n">
@@ -14538,17 +14538,17 @@
         </is>
       </c>
       <c r="I134" s="4" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="J134" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K134" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L134" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-9</v>
+      </c>
+      <c r="L134" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M134" s="8" t="n">
@@ -14643,17 +14643,17 @@
         </is>
       </c>
       <c r="I135" s="4" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="J135" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K135" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L135" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-14</v>
+      </c>
+      <c r="L135" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M135" s="8" t="n">
@@ -14748,17 +14748,17 @@
         </is>
       </c>
       <c r="I136" s="4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J136" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K136" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L136" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-1</v>
+      </c>
+      <c r="L136" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M136" s="8" t="n">
@@ -14793,7 +14793,7 @@
         <v>0</v>
       </c>
       <c r="V136" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W136" s="9" t="n">
         <v>0</v>
@@ -14853,13 +14853,13 @@
         </is>
       </c>
       <c r="I137" s="4" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J137" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K137" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L137" s="4" t="inlineStr">
         <is>
@@ -14901,7 +14901,7 @@
         <v>4</v>
       </c>
       <c r="W137" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X137" s="10" t="n">
         <v>5</v>
@@ -14944,7 +14944,7 @@
         </is>
       </c>
       <c r="E138" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F138" s="6" t="n">
         <v>10</v>
@@ -14958,13 +14958,13 @@
         </is>
       </c>
       <c r="I138" s="4" t="n">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="J138" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K138" s="4" t="n">
-        <v>2</v>
+        <v>-11</v>
       </c>
       <c r="L138" s="4" t="inlineStr">
         <is>
@@ -14985,10 +14985,10 @@
         </is>
       </c>
       <c r="P138" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q138" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R138" s="9" t="n">
         <v>0</v>
@@ -15002,8 +15002,8 @@
       <c r="U138" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V138" s="9" t="n">
-        <v>2</v>
+      <c r="V138" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W138" s="9" t="n">
         <v>0</v>
@@ -15063,17 +15063,17 @@
         </is>
       </c>
       <c r="I139" s="4" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J139" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K139" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L139" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L139" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M139" s="8" t="n">
@@ -15168,17 +15168,17 @@
         </is>
       </c>
       <c r="I140" s="4" t="n">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="J140" s="4" t="n">
         <v>34</v>
       </c>
       <c r="K140" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L140" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-18</v>
+      </c>
+      <c r="L140" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M140" s="8" t="n">
@@ -15213,7 +15213,7 @@
         <v>0</v>
       </c>
       <c r="V140" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W140" s="9" t="n">
         <v>0</v>
@@ -15269,13 +15269,13 @@
         </is>
       </c>
       <c r="I141" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J141" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K141" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L141" s="7" t="inlineStr">
         <is>
@@ -15370,13 +15370,13 @@
         </is>
       </c>
       <c r="I142" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J142" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K142" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L142" s="7" t="inlineStr">
         <is>
@@ -15471,13 +15471,13 @@
         </is>
       </c>
       <c r="I143" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J143" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K143" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L143" s="7" t="inlineStr">
         <is>
@@ -15516,7 +15516,7 @@
         <v>0</v>
       </c>
       <c r="V143" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W143" s="9" t="n">
         <v>0</v>
@@ -15572,17 +15572,17 @@
         </is>
       </c>
       <c r="I144" s="4" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="J144" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K144" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L144" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-16</v>
+      </c>
+      <c r="L144" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M144" s="8" t="n">
@@ -15677,17 +15677,17 @@
         </is>
       </c>
       <c r="I145" s="4" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J145" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K145" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L145" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L145" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M145" s="8" t="n">
@@ -15782,17 +15782,17 @@
         </is>
       </c>
       <c r="I146" s="4" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J146" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K146" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L146" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L146" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M146" s="8" t="n">
@@ -15827,7 +15827,7 @@
         <v>0</v>
       </c>
       <c r="V146" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W146" s="9" t="n">
         <v>0</v>
@@ -15887,13 +15887,13 @@
         </is>
       </c>
       <c r="I147" s="4" t="n">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="J147" s="4" t="n">
         <v>128</v>
       </c>
       <c r="K147" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L147" s="4" t="inlineStr">
         <is>
@@ -15932,7 +15932,7 @@
         <v>0</v>
       </c>
       <c r="V147" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W147" s="9" t="n">
         <v>0</v>
@@ -16089,17 +16089,17 @@
         </is>
       </c>
       <c r="I149" s="4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J149" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K149" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L149" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>3</v>
+      </c>
+      <c r="L149" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M149" s="8" t="n">
@@ -16190,17 +16190,17 @@
         </is>
       </c>
       <c r="I150" s="4" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J150" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K150" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L150" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L150" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M150" s="8" t="n">
@@ -16291,13 +16291,13 @@
         </is>
       </c>
       <c r="I151" s="4" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J151" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K151" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L151" s="4" t="inlineStr">
         <is>
@@ -16318,7 +16318,7 @@
         </is>
       </c>
       <c r="P151" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q151" s="9" t="n">
         <v>0</v>
@@ -16396,13 +16396,13 @@
         </is>
       </c>
       <c r="I152" s="4" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="J152" s="4" t="n">
         <v>34</v>
       </c>
       <c r="K152" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L152" s="4" t="inlineStr">
         <is>
@@ -16501,13 +16501,13 @@
         </is>
       </c>
       <c r="I153" s="4" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="J153" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K153" s="4" t="n">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="L153" s="4" t="inlineStr">
         <is>
@@ -16606,17 +16606,17 @@
         </is>
       </c>
       <c r="I154" s="4" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J154" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K154" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L154" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L154" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M154" s="8" t="n">
@@ -16651,7 +16651,7 @@
         <v>1</v>
       </c>
       <c r="V154" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W154" s="9" t="n">
         <v>0</v>
@@ -16711,13 +16711,13 @@
         </is>
       </c>
       <c r="I155" s="4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J155" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K155" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L155" s="7" t="inlineStr">
         <is>
@@ -16913,17 +16913,17 @@
         </is>
       </c>
       <c r="I157" s="4" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="J157" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K157" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L157" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L157" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M157" s="8" t="n">
@@ -17105,7 +17105,7 @@
         </is>
       </c>
       <c r="E159" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F159" s="6" t="n">
         <v>10</v>
@@ -17119,17 +17119,17 @@
         </is>
       </c>
       <c r="I159" s="4" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="J159" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K159" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L159" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>5</v>
+      </c>
+      <c r="L159" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M159" s="8" t="n">
@@ -17163,11 +17163,11 @@
       <c r="U159" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V159" s="9" t="n">
-        <v>1</v>
+      <c r="V159" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W159" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X159" s="9" t="n">
         <v>0</v>
@@ -17220,17 +17220,17 @@
         </is>
       </c>
       <c r="I160" s="4" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="J160" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K160" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L160" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L160" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M160" s="8" t="n">
@@ -17325,13 +17325,13 @@
         </is>
       </c>
       <c r="I161" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J161" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K161" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L161" s="7" t="inlineStr">
         <is>
@@ -17370,7 +17370,7 @@
         <v>0</v>
       </c>
       <c r="V161" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W161" s="9" t="n">
         <v>0</v>
@@ -17426,17 +17426,17 @@
         </is>
       </c>
       <c r="I162" s="4" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="J162" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K162" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L162" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L162" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M162" s="8" t="n">
@@ -17531,17 +17531,17 @@
         </is>
       </c>
       <c r="I163" s="4" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="J163" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K163" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L163" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L163" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M163" s="8" t="n">
@@ -17737,13 +17737,13 @@
         </is>
       </c>
       <c r="I165" s="4" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="J165" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K165" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L165" s="4" t="inlineStr">
         <is>
@@ -17828,7 +17828,7 @@
         </is>
       </c>
       <c r="E166" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F166" s="6" t="n">
         <v>10</v>
@@ -17842,17 +17842,17 @@
         </is>
       </c>
       <c r="I166" s="4" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J166" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K166" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L166" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L166" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M166" s="8" t="n">
@@ -17886,8 +17886,8 @@
       <c r="U166" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V166" s="9" t="n">
-        <v>0</v>
+      <c r="V166" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W166" s="9" t="n">
         <v>0</v>
@@ -17947,13 +17947,13 @@
         </is>
       </c>
       <c r="I167" s="4" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="J167" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K167" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L167" s="4" t="inlineStr">
         <is>
@@ -18052,13 +18052,13 @@
         </is>
       </c>
       <c r="I168" s="4" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="J168" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K168" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L168" s="7" t="inlineStr">
         <is>
@@ -18153,13 +18153,13 @@
         </is>
       </c>
       <c r="I169" s="4" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="J169" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K169" s="4" t="n">
-        <v>3</v>
+        <v>-6</v>
       </c>
       <c r="L169" s="7" t="inlineStr">
         <is>
@@ -18254,13 +18254,13 @@
         </is>
       </c>
       <c r="I170" s="4" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J170" s="4" t="n">
         <v>42</v>
       </c>
       <c r="K170" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L170" s="4" t="inlineStr">
         <is>
@@ -18281,7 +18281,7 @@
         </is>
       </c>
       <c r="P170" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q170" s="9" t="n">
         <v>0</v>
@@ -18359,13 +18359,13 @@
         </is>
       </c>
       <c r="I171" s="4" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J171" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K171" s="4" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="L171" s="4" t="inlineStr">
         <is>
@@ -18404,7 +18404,7 @@
         <v>0</v>
       </c>
       <c r="V171" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W171" s="9" t="n">
         <v>0</v>
@@ -18464,17 +18464,17 @@
         </is>
       </c>
       <c r="I172" s="4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="J172" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K172" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L172" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L172" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M172" s="8" t="n">
@@ -18569,13 +18569,13 @@
         </is>
       </c>
       <c r="I173" s="4" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J173" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K173" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L173" s="4" t="inlineStr">
         <is>
@@ -18660,7 +18660,7 @@
         </is>
       </c>
       <c r="E174" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F174" s="6" t="n">
         <v>10</v>
@@ -18674,13 +18674,13 @@
         </is>
       </c>
       <c r="I174" s="4" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="J174" s="4" t="n">
         <v>45</v>
       </c>
       <c r="K174" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L174" s="4" t="inlineStr">
         <is>
@@ -18721,8 +18721,8 @@
       <c r="V174" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W174" s="9" t="n">
-        <v>1</v>
+      <c r="W174" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X174" s="10" t="n">
         <v>7</v>
@@ -18779,17 +18779,17 @@
         </is>
       </c>
       <c r="I175" s="4" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="J175" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K175" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L175" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L175" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M175" s="8" t="n">
@@ -18884,17 +18884,17 @@
         </is>
       </c>
       <c r="I176" s="4" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J176" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K176" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L176" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L176" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M176" s="8" t="n">
@@ -18989,13 +18989,13 @@
         </is>
       </c>
       <c r="I177" s="4" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J177" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K177" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L177" s="4" t="inlineStr">
         <is>
@@ -19094,17 +19094,17 @@
         </is>
       </c>
       <c r="I178" s="4" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="J178" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K178" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L178" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L178" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M178" s="8" t="n">
@@ -19304,13 +19304,13 @@
         </is>
       </c>
       <c r="I180" s="4" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J180" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K180" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L180" s="4" t="inlineStr">
         <is>
@@ -19409,13 +19409,13 @@
         </is>
       </c>
       <c r="I181" s="4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J181" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K181" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L181" s="7" t="inlineStr">
         <is>
@@ -19454,7 +19454,7 @@
         <v>0</v>
       </c>
       <c r="V181" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W181" s="9" t="n">
         <v>0</v>
@@ -19496,7 +19496,7 @@
         </is>
       </c>
       <c r="E182" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F182" s="6" t="n">
         <v>10</v>
@@ -19510,13 +19510,13 @@
         </is>
       </c>
       <c r="I182" s="4" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J182" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K182" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L182" s="4" t="inlineStr">
         <is>
@@ -19554,8 +19554,8 @@
       <c r="U182" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V182" s="9" t="n">
-        <v>1</v>
+      <c r="V182" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W182" s="9" t="n">
         <v>0</v>
@@ -19615,13 +19615,13 @@
         </is>
       </c>
       <c r="I183" s="4" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="J183" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K183" s="4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L183" s="4" t="inlineStr">
         <is>
@@ -19716,17 +19716,17 @@
         </is>
       </c>
       <c r="I184" s="4" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J184" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K184" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L184" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L184" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M184" s="8" t="n">
@@ -19821,13 +19821,13 @@
         </is>
       </c>
       <c r="I185" s="4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J185" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K185" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L185" s="7" t="inlineStr">
         <is>
@@ -19866,7 +19866,7 @@
         <v>0</v>
       </c>
       <c r="V185" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W185" s="9" t="n">
         <v>0</v>
@@ -19912,7 +19912,7 @@
         </is>
       </c>
       <c r="E186" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F186" s="6" t="n">
         <v>10</v>
@@ -19926,13 +19926,13 @@
         </is>
       </c>
       <c r="I186" s="4" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="J186" s="4" t="n">
         <v>49</v>
       </c>
       <c r="K186" s="4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L186" s="4" t="inlineStr">
         <is>
@@ -19973,8 +19973,8 @@
       <c r="V186" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W186" s="9" t="n">
-        <v>3</v>
+      <c r="W186" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X186" s="10" t="n">
         <v>5</v>
@@ -20031,13 +20031,13 @@
         </is>
       </c>
       <c r="I187" s="4" t="n">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="J187" s="4" t="n">
         <v>45</v>
       </c>
       <c r="K187" s="4" t="n">
-        <v>9</v>
+        <v>-1</v>
       </c>
       <c r="L187" s="4" t="inlineStr">
         <is>
@@ -20122,7 +20122,7 @@
         </is>
       </c>
       <c r="E188" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F188" s="6" t="n">
         <v>10</v>
@@ -20136,13 +20136,13 @@
         </is>
       </c>
       <c r="I188" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J188" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K188" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L188" s="4" t="inlineStr">
         <is>
@@ -20180,8 +20180,8 @@
       <c r="U188" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="V188" s="9" t="n">
-        <v>0</v>
+      <c r="V188" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W188" s="9" t="n">
         <v>0</v>
@@ -20241,13 +20241,13 @@
         </is>
       </c>
       <c r="I189" s="4" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="J189" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K189" s="4" t="n">
-        <v>2</v>
+        <v>-4</v>
       </c>
       <c r="L189" s="4" t="inlineStr">
         <is>
@@ -20346,13 +20346,13 @@
         </is>
       </c>
       <c r="I190" s="4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J190" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K190" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L190" s="4" t="inlineStr">
         <is>
@@ -20447,13 +20447,13 @@
         </is>
       </c>
       <c r="I191" s="4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J191" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K191" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L191" s="7" t="inlineStr">
         <is>
@@ -20534,7 +20534,7 @@
         </is>
       </c>
       <c r="E192" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F192" s="6" t="n">
         <v>10</v>
@@ -20548,13 +20548,13 @@
         </is>
       </c>
       <c r="I192" s="4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J192" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K192" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L192" s="4" t="inlineStr">
         <is>
@@ -20595,8 +20595,8 @@
       <c r="V192" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W192" s="9" t="n">
-        <v>3</v>
+      <c r="W192" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X192" s="10" t="n">
         <v>7</v>
@@ -20649,13 +20649,13 @@
         </is>
       </c>
       <c r="I193" s="4" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="J193" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K193" s="4" t="n">
-        <v>1</v>
+        <v>-6</v>
       </c>
       <c r="L193" s="7" t="inlineStr">
         <is>
@@ -20754,13 +20754,13 @@
         </is>
       </c>
       <c r="I194" s="4" t="n">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="J194" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K194" s="4" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="L194" s="4" t="inlineStr">
         <is>
@@ -20781,7 +20781,7 @@
         </is>
       </c>
       <c r="P194" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q194" s="10" t="n">
         <v>2</v>
@@ -20790,7 +20790,7 @@
         <v>1</v>
       </c>
       <c r="S194" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T194" s="10" t="n">
         <v>1</v>
@@ -20802,7 +20802,7 @@
         <v>4</v>
       </c>
       <c r="W194" s="10" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="X194" s="10" t="n">
         <v>7</v>
@@ -20845,7 +20845,7 @@
         </is>
       </c>
       <c r="E195" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F195" s="6" t="n">
         <v>10</v>
@@ -20859,13 +20859,13 @@
         </is>
       </c>
       <c r="I195" s="4" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J195" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K195" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L195" s="4" t="inlineStr">
         <is>
@@ -20904,7 +20904,7 @@
         <v>0</v>
       </c>
       <c r="V195" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W195" s="9" t="n">
         <v>0</v>
@@ -20915,8 +20915,8 @@
       <c r="Y195" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z195" s="9" t="n">
-        <v>0</v>
+      <c r="Z195" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA195" s="10" t="n">
         <v>1</v>
@@ -20958,13 +20958,13 @@
         </is>
       </c>
       <c r="I196" s="4" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J196" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K196" s="4" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
       <c r="L196" s="7" t="inlineStr">
         <is>
@@ -21059,13 +21059,13 @@
         </is>
       </c>
       <c r="I197" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J197" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K197" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L197" s="7" t="inlineStr">
         <is>
@@ -21160,13 +21160,13 @@
         </is>
       </c>
       <c r="I198" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J198" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K198" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L198" s="7" t="inlineStr">
         <is>
@@ -21205,7 +21205,7 @@
         <v>0</v>
       </c>
       <c r="V198" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W198" s="9" t="n">
         <v>0</v>
@@ -21265,17 +21265,17 @@
         </is>
       </c>
       <c r="I199" s="4" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="J199" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K199" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L199" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-25</v>
+      </c>
+      <c r="L199" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M199" s="8" t="n">
@@ -21370,17 +21370,17 @@
         </is>
       </c>
       <c r="I200" s="4" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J200" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K200" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L200" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L200" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M200" s="8" t="n">
@@ -21461,7 +21461,7 @@
         </is>
       </c>
       <c r="E201" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F201" s="6" t="n">
         <v>10</v>
@@ -21475,13 +21475,13 @@
         </is>
       </c>
       <c r="I201" s="4" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="J201" s="4" t="n">
         <v>35</v>
       </c>
       <c r="K201" s="4" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="L201" s="4" t="inlineStr">
         <is>
@@ -21502,7 +21502,7 @@
         </is>
       </c>
       <c r="P201" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q201" s="9" t="n">
         <v>1</v>
@@ -21519,11 +21519,11 @@
       <c r="U201" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="V201" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="W201" s="9" t="n">
-        <v>0</v>
+      <c r="V201" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W201" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X201" s="10" t="n">
         <v>7</v>
@@ -21580,13 +21580,13 @@
         </is>
       </c>
       <c r="I202" s="4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J202" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K202" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L202" s="4" t="inlineStr">
         <is>
@@ -21625,7 +21625,7 @@
         <v>0</v>
       </c>
       <c r="V202" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W202" s="9" t="n">
         <v>0</v>
@@ -21685,13 +21685,13 @@
         </is>
       </c>
       <c r="I203" s="4" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="J203" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K203" s="4" t="n">
-        <v>2</v>
+        <v>-4</v>
       </c>
       <c r="L203" s="7" t="inlineStr">
         <is>
@@ -21891,17 +21891,17 @@
         </is>
       </c>
       <c r="I205" s="4" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J205" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K205" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L205" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L205" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M205" s="8" t="n">
@@ -21936,7 +21936,7 @@
         <v>1</v>
       </c>
       <c r="V205" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W205" s="9" t="n">
         <v>0</v>
@@ -22097,13 +22097,13 @@
         </is>
       </c>
       <c r="I207" s="4" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="J207" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K207" s="4" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="L207" s="7" t="inlineStr">
         <is>
@@ -22198,13 +22198,13 @@
         </is>
       </c>
       <c r="I208" s="4" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="J208" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K208" s="4" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="L208" s="4" t="inlineStr">
         <is>
@@ -22231,7 +22231,7 @@
         <v>2</v>
       </c>
       <c r="R208" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S208" s="10" t="n">
         <v>2</v>
@@ -22243,7 +22243,7 @@
         <v>2</v>
       </c>
       <c r="V208" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W208" s="9" t="n">
         <v>0</v>
@@ -22289,7 +22289,7 @@
         </is>
       </c>
       <c r="E209" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F209" s="6" t="n">
         <v>10</v>
@@ -22303,13 +22303,13 @@
         </is>
       </c>
       <c r="I209" s="4" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="J209" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K209" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L209" s="4" t="inlineStr">
         <is>
@@ -22329,8 +22329,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P209" s="9" t="n">
-        <v>3</v>
+      <c r="P209" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q209" s="10" t="n">
         <v>2</v>
@@ -22351,7 +22351,7 @@
         <v>4</v>
       </c>
       <c r="W209" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X209" s="10" t="n">
         <v>7</v>
@@ -22408,13 +22408,13 @@
         </is>
       </c>
       <c r="I210" s="4" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J210" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K210" s="4" t="n">
-        <v>3</v>
+        <v>-2</v>
       </c>
       <c r="L210" s="4" t="inlineStr">
         <is>
@@ -22513,13 +22513,13 @@
         </is>
       </c>
       <c r="I211" s="4" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J211" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K211" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L211" s="4" t="inlineStr">
         <is>
@@ -22618,13 +22618,13 @@
         </is>
       </c>
       <c r="I212" s="4" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J212" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K212" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L212" s="7" t="inlineStr">
         <is>
@@ -22705,7 +22705,7 @@
         </is>
       </c>
       <c r="E213" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F213" s="6" t="n">
         <v>10</v>
@@ -22719,17 +22719,17 @@
         </is>
       </c>
       <c r="I213" s="4" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="J213" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K213" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L213" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L213" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M213" s="8" t="n">
@@ -22746,7 +22746,7 @@
         </is>
       </c>
       <c r="P213" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q213" s="9" t="n">
         <v>1</v>
@@ -22763,8 +22763,8 @@
       <c r="U213" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V213" s="10" t="n">
-        <v>4</v>
+      <c r="V213" s="9" t="n">
+        <v>3</v>
       </c>
       <c r="W213" s="9" t="n">
         <v>0</v>
@@ -22925,13 +22925,13 @@
         </is>
       </c>
       <c r="I215" s="4" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="J215" s="4" t="n">
         <v>45</v>
       </c>
       <c r="K215" s="4" t="n">
-        <v>5</v>
+        <v>-7</v>
       </c>
       <c r="L215" s="4" t="inlineStr">
         <is>
@@ -22973,7 +22973,7 @@
         <v>4</v>
       </c>
       <c r="W215" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X215" s="10" t="n">
         <v>7</v>
@@ -23016,7 +23016,7 @@
         </is>
       </c>
       <c r="E216" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F216" s="6" t="n">
         <v>10</v>
@@ -23030,13 +23030,13 @@
         </is>
       </c>
       <c r="I216" s="4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J216" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K216" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L216" s="7" t="inlineStr">
         <is>
@@ -23074,8 +23074,8 @@
       <c r="U216" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V216" s="9" t="n">
-        <v>3</v>
+      <c r="V216" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W216" s="9" t="n">
         <v>0</v>
@@ -23131,13 +23131,13 @@
         </is>
       </c>
       <c r="I217" s="4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J217" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K217" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L217" s="7" t="inlineStr">
         <is>
@@ -23232,13 +23232,13 @@
         </is>
       </c>
       <c r="I218" s="4" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J218" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K218" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L218" s="4" t="inlineStr">
         <is>
@@ -23492,7 +23492,7 @@
         <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -23507,7 +23507,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -23525,7 +23525,7 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
@@ -23540,7 +23540,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -23606,7 +23606,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -23639,7 +23639,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -23657,7 +23657,7 @@
         <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>2.5</v>
+        <v>3.25</v>
       </c>
       <c r="E7" t="n">
         <v>1</v>
@@ -23672,7 +23672,7 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -23690,7 +23690,7 @@
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -23705,7 +23705,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -23723,7 +23723,7 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E9" t="n">
         <v>1</v>
@@ -23738,7 +23738,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -23756,7 +23756,7 @@
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="E10" t="n">
         <v>1</v>
@@ -23789,7 +23789,7 @@
         <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -23804,7 +23804,7 @@
         <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -23837,7 +23837,7 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
@@ -23855,13 +23855,13 @@
         <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>1.83</v>
+        <v>2.17</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -23870,7 +23870,7 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -23903,7 +23903,7 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -23936,7 +23936,7 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -23969,7 +23969,7 @@
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -23987,7 +23987,7 @@
         <v>6</v>
       </c>
       <c r="D17" t="n">
-        <v>3</v>
+        <v>3.17</v>
       </c>
       <c r="E17" t="n">
         <v>1</v>
@@ -24002,7 +24002,7 @@
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18">
@@ -24035,7 +24035,7 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -24053,7 +24053,7 @@
         <v>4</v>
       </c>
       <c r="D19" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -24068,7 +24068,7 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -24086,7 +24086,7 @@
         <v>5</v>
       </c>
       <c r="D20" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -24101,7 +24101,7 @@
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -24119,7 +24119,7 @@
         <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -24134,7 +24134,7 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -24152,7 +24152,7 @@
         <v>4</v>
       </c>
       <c r="D22" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -24167,7 +24167,7 @@
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -24200,7 +24200,7 @@
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -24233,7 +24233,7 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -24251,7 +24251,7 @@
         <v>5</v>
       </c>
       <c r="D25" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="E25" t="n">
         <v>1</v>
@@ -24266,7 +24266,7 @@
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26">
@@ -24284,13 +24284,13 @@
         <v>5</v>
       </c>
       <c r="D26" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -24299,7 +24299,7 @@
         <v>1</v>
       </c>
       <c r="I26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -24317,7 +24317,7 @@
         <v>4</v>
       </c>
       <c r="D27" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -24398,7 +24398,7 @@
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -24416,7 +24416,7 @@
         <v>4</v>
       </c>
       <c r="D30" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -24431,7 +24431,7 @@
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -24464,7 +24464,7 @@
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -24497,7 +24497,7 @@
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -24530,7 +24530,7 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -24563,7 +24563,7 @@
         <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -24581,7 +24581,7 @@
         <v>5</v>
       </c>
       <c r="D35" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
@@ -24596,7 +24596,7 @@
         <v>2</v>
       </c>
       <c r="I35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -24614,7 +24614,7 @@
         <v>5</v>
       </c>
       <c r="D36" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
@@ -24629,7 +24629,7 @@
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37">
@@ -24662,7 +24662,7 @@
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -24680,7 +24680,7 @@
         <v>4</v>
       </c>
       <c r="D38" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
@@ -24695,7 +24695,7 @@
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39">
@@ -24728,7 +24728,7 @@
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="40">
@@ -24746,13 +24746,13 @@
         <v>6</v>
       </c>
       <c r="D40" t="n">
-        <v>2.17</v>
+        <v>2.5</v>
       </c>
       <c r="E40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F40" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -24761,7 +24761,7 @@
         <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="41">
@@ -24779,7 +24779,7 @@
         <v>5</v>
       </c>
       <c r="D41" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="E41" t="n">
         <v>1</v>
@@ -24812,7 +24812,7 @@
         <v>7</v>
       </c>
       <c r="D42" t="n">
-        <v>2.57</v>
+        <v>2.86</v>
       </c>
       <c r="E42" t="n">
         <v>2</v>
@@ -24845,13 +24845,13 @@
         <v>5</v>
       </c>
       <c r="D43" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F43" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -24860,7 +24860,7 @@
         <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -24878,7 +24878,7 @@
         <v>6</v>
       </c>
       <c r="D44" t="n">
-        <v>3.33</v>
+        <v>3.5</v>
       </c>
       <c r="E44" t="n">
         <v>2</v>
@@ -24893,7 +24893,7 @@
         <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="45">
@@ -24911,7 +24911,7 @@
         <v>5</v>
       </c>
       <c r="D45" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="E45" t="n">
         <v>0</v>
@@ -24926,7 +24926,7 @@
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -24944,7 +24944,7 @@
         <v>5</v>
       </c>
       <c r="D46" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E46" t="n">
         <v>0</v>

--- a/docs/d/80/inyear.xlsx
+++ b/docs/d/80/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:39 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/80/inyear.xlsx
+++ b/docs/d/80/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:39 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/80/inyear.xlsx
+++ b/docs/d/80/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/80/inyear.xlsx
+++ b/docs/d/80/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/80/inyear.xlsx
+++ b/docs/d/80/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>262 days remain until 30 June 2027, when these scores become final.</t>
+          <t>255 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 5 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 5 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 21 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 21 clubs short</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
         <v>0</v>
       </c>
       <c r="S14" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T14" s="9" t="n">
         <v>0</v>
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="E17" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F17" s="6" t="n">
         <v>10</v>
@@ -2401,13 +2401,13 @@
         </is>
       </c>
       <c r="I17" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J17" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L17" s="7" t="inlineStr">
         <is>
@@ -2442,11 +2442,11 @@
       <c r="T17" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U17" s="9" t="n">
-        <v>0</v>
+      <c r="U17" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V17" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W17" s="9" t="n">
         <v>0</v>
@@ -2603,13 +2603,13 @@
         </is>
       </c>
       <c r="I19" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J19" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L19" s="7" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
         <v>0</v>
       </c>
       <c r="V19" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W19" s="9" t="n">
         <v>0</v>
@@ -3019,13 +3019,13 @@
         </is>
       </c>
       <c r="I23" s="4" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J23" s="4" t="n">
         <v>58</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L23" s="4" t="inlineStr">
         <is>
@@ -3046,7 +3046,7 @@
         </is>
       </c>
       <c r="P23" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q23" s="9" t="n">
         <v>1</v>
@@ -3067,7 +3067,7 @@
         <v>4</v>
       </c>
       <c r="W23" s="10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="X23" s="10" t="n">
         <v>7</v>
@@ -3540,13 +3540,13 @@
         </is>
       </c>
       <c r="I28" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J28" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L28" s="4" t="inlineStr">
         <is>
@@ -3942,7 +3942,7 @@
         </is>
       </c>
       <c r="E32" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F32" s="6" t="n">
         <v>10</v>
@@ -3997,8 +3997,8 @@
       <c r="T32" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U32" s="9" t="n">
-        <v>0</v>
+      <c r="U32" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V32" s="9" t="n">
         <v>2</v>
@@ -5218,7 +5218,7 @@
         <v>1</v>
       </c>
       <c r="Q44" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R44" s="9" t="n">
         <v>0</v>
@@ -6268,7 +6268,7 @@
         <v>1</v>
       </c>
       <c r="U54" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V54" s="10" t="n">
         <v>4</v>
@@ -7093,10 +7093,10 @@
         </is>
       </c>
       <c r="P62" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q62" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R62" s="9" t="n">
         <v>0</v>
@@ -7573,7 +7573,7 @@
         </is>
       </c>
       <c r="E67" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F67" s="6" t="n">
         <v>10</v>
@@ -7587,13 +7587,13 @@
         </is>
       </c>
       <c r="I67" s="4" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J67" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>-8</v>
+        <v>-5</v>
       </c>
       <c r="L67" s="7" t="inlineStr">
         <is>
@@ -7631,11 +7631,11 @@
       <c r="U67" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V67" s="9" t="n">
-        <v>3</v>
+      <c r="V67" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W67" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X67" s="10" t="n">
         <v>7</v>
@@ -8243,7 +8243,7 @@
         <v>0</v>
       </c>
       <c r="Q73" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R73" s="9" t="n">
         <v>0</v>
@@ -8660,7 +8660,7 @@
         </is>
       </c>
       <c r="P77" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q77" s="10" t="n">
         <v>2</v>
@@ -8765,7 +8765,7 @@
         </is>
       </c>
       <c r="P78" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q78" s="9" t="n">
         <v>0</v>
@@ -8774,7 +8774,7 @@
         <v>0</v>
       </c>
       <c r="S78" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T78" s="9" t="n">
         <v>0</v>
@@ -10806,13 +10806,13 @@
         </is>
       </c>
       <c r="I98" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J98" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K98" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L98" s="7" t="inlineStr">
         <is>
@@ -12182,7 +12182,7 @@
         </is>
       </c>
       <c r="P111" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q111" s="9" t="n">
         <v>1</v>
@@ -12395,7 +12395,7 @@
         <v>0</v>
       </c>
       <c r="Q113" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R113" s="9" t="n">
         <v>0</v>
@@ -12872,7 +12872,7 @@
         </is>
       </c>
       <c r="E118" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F118" s="6" t="n">
         <v>10</v>
@@ -12886,13 +12886,13 @@
         </is>
       </c>
       <c r="I118" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J118" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K118" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L118" s="7" t="inlineStr">
         <is>
@@ -12930,8 +12930,8 @@
       <c r="U118" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V118" s="9" t="n">
-        <v>3</v>
+      <c r="V118" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W118" s="9" t="n">
         <v>0</v>
@@ -13435,7 +13435,7 @@
         <v>0</v>
       </c>
       <c r="S123" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T123" s="9" t="n">
         <v>0</v>
@@ -13504,13 +13504,13 @@
         </is>
       </c>
       <c r="I124" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J124" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K124" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L124" s="7" t="inlineStr">
         <is>
@@ -13591,7 +13591,7 @@
         </is>
       </c>
       <c r="E125" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F125" s="6" t="n">
         <v>10</v>
@@ -13646,8 +13646,8 @@
       <c r="T125" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U125" s="9" t="n">
-        <v>0</v>
+      <c r="U125" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V125" s="10" t="n">
         <v>4</v>
@@ -13706,13 +13706,13 @@
         </is>
       </c>
       <c r="I126" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J126" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K126" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L126" s="4" t="inlineStr">
         <is>
@@ -13751,7 +13751,7 @@
         <v>0</v>
       </c>
       <c r="V126" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W126" s="9" t="n">
         <v>0</v>
@@ -14227,13 +14227,13 @@
         </is>
       </c>
       <c r="I131" s="4" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J131" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K131" s="4" t="n">
-        <v>-13</v>
+        <v>-10</v>
       </c>
       <c r="L131" s="7" t="inlineStr">
         <is>
@@ -14272,7 +14272,7 @@
         <v>0</v>
       </c>
       <c r="V131" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W131" s="9" t="n">
         <v>0</v>
@@ -14853,13 +14853,13 @@
         </is>
       </c>
       <c r="I137" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J137" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K137" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L137" s="4" t="inlineStr">
         <is>
@@ -14901,7 +14901,7 @@
         <v>4</v>
       </c>
       <c r="W137" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X137" s="10" t="n">
         <v>5</v>
@@ -15663,7 +15663,7 @@
         </is>
       </c>
       <c r="E145" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F145" s="6" t="n">
         <v>10</v>
@@ -15706,8 +15706,8 @@
       <c r="P145" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q145" s="9" t="n">
-        <v>0</v>
+      <c r="Q145" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R145" s="9" t="n">
         <v>0</v>
@@ -16432,7 +16432,7 @@
         <v>0</v>
       </c>
       <c r="S152" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T152" s="9" t="n">
         <v>0</v>
@@ -16501,13 +16501,13 @@
         </is>
       </c>
       <c r="I153" s="4" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J153" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K153" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L153" s="4" t="inlineStr">
         <is>
@@ -16549,7 +16549,7 @@
         <v>4</v>
       </c>
       <c r="W153" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X153" s="10" t="n">
         <v>7</v>
@@ -16633,10 +16633,10 @@
         </is>
       </c>
       <c r="P154" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q154" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R154" s="9" t="n">
         <v>0</v>
@@ -17558,7 +17558,7 @@
         </is>
       </c>
       <c r="P163" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q163" s="9" t="n">
         <v>0</v>
@@ -17842,13 +17842,13 @@
         </is>
       </c>
       <c r="I166" s="4" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J166" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K166" s="4" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="L166" s="7" t="inlineStr">
         <is>
@@ -17869,7 +17869,7 @@
         </is>
       </c>
       <c r="P166" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q166" s="9" t="n">
         <v>0</v>
@@ -17890,7 +17890,7 @@
         <v>4</v>
       </c>
       <c r="W166" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X166" s="10" t="n">
         <v>6</v>
@@ -18038,7 +18038,7 @@
         </is>
       </c>
       <c r="E168" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F168" s="6" t="n">
         <v>10</v>
@@ -18090,8 +18090,8 @@
       <c r="S168" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T168" s="9" t="n">
-        <v>0</v>
+      <c r="T168" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U168" s="9" t="n">
         <v>0</v>
@@ -18359,13 +18359,13 @@
         </is>
       </c>
       <c r="I171" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J171" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K171" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L171" s="4" t="inlineStr">
         <is>
@@ -18404,7 +18404,7 @@
         <v>0</v>
       </c>
       <c r="V171" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W171" s="9" t="n">
         <v>0</v>
@@ -18569,13 +18569,13 @@
         </is>
       </c>
       <c r="I173" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J173" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K173" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L173" s="4" t="inlineStr">
         <is>
@@ -18614,7 +18614,7 @@
         <v>0</v>
       </c>
       <c r="V173" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W173" s="9" t="n">
         <v>0</v>
@@ -19290,7 +19290,7 @@
         </is>
       </c>
       <c r="E180" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F180" s="6" t="n">
         <v>10</v>
@@ -19331,10 +19331,10 @@
         </is>
       </c>
       <c r="P180" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q180" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R180" s="9" t="n">
         <v>0</v>
@@ -19345,8 +19345,8 @@
       <c r="T180" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U180" s="9" t="n">
-        <v>0</v>
+      <c r="U180" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V180" s="9" t="n">
         <v>1</v>
@@ -19537,7 +19537,7 @@
         </is>
       </c>
       <c r="P182" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q182" s="9" t="n">
         <v>0</v>
@@ -20534,7 +20534,7 @@
         </is>
       </c>
       <c r="E192" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F192" s="6" t="n">
         <v>10</v>
@@ -20574,8 +20574,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P192" s="9" t="n">
-        <v>3</v>
+      <c r="P192" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q192" s="10" t="n">
         <v>2</v>
@@ -21059,13 +21059,13 @@
         </is>
       </c>
       <c r="I197" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J197" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K197" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L197" s="7" t="inlineStr">
         <is>
@@ -21104,7 +21104,7 @@
         <v>0</v>
       </c>
       <c r="V197" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W197" s="9" t="n">
         <v>0</v>
@@ -21475,13 +21475,13 @@
         </is>
       </c>
       <c r="I201" s="4" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J201" s="4" t="n">
         <v>35</v>
       </c>
       <c r="K201" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L201" s="4" t="inlineStr">
         <is>
@@ -21523,7 +21523,7 @@
         <v>4</v>
       </c>
       <c r="W201" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X201" s="10" t="n">
         <v>7</v>
@@ -22184,7 +22184,7 @@
         </is>
       </c>
       <c r="E208" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F208" s="6" t="n">
         <v>10</v>
@@ -22224,8 +22224,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P208" s="9" t="n">
-        <v>3</v>
+      <c r="P208" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q208" s="10" t="n">
         <v>2</v>
@@ -22289,7 +22289,7 @@
         </is>
       </c>
       <c r="E209" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F209" s="6" t="n">
         <v>10</v>
@@ -22303,13 +22303,13 @@
         </is>
       </c>
       <c r="I209" s="4" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J209" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K209" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L209" s="4" t="inlineStr">
         <is>
@@ -22350,8 +22350,8 @@
       <c r="V209" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W209" s="9" t="n">
-        <v>3</v>
+      <c r="W209" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X209" s="10" t="n">
         <v>7</v>
@@ -23591,7 +23591,7 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -23723,7 +23723,7 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E9" t="n">
         <v>1</v>
@@ -23921,7 +23921,7 @@
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="E15" t="n">
         <v>1</v>
@@ -24284,7 +24284,7 @@
         <v>5</v>
       </c>
       <c r="D26" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="E26" t="n">
         <v>1</v>
@@ -24317,7 +24317,7 @@
         <v>4</v>
       </c>
       <c r="D27" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -24482,7 +24482,7 @@
         <v>4</v>
       </c>
       <c r="D32" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
@@ -24647,7 +24647,7 @@
         <v>5</v>
       </c>
       <c r="D37" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>
@@ -24713,7 +24713,7 @@
         <v>4</v>
       </c>
       <c r="D39" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="E39" t="n">
         <v>1</v>
@@ -24812,7 +24812,7 @@
         <v>7</v>
       </c>
       <c r="D42" t="n">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="E42" t="n">
         <v>2</v>
@@ -24878,7 +24878,7 @@
         <v>6</v>
       </c>
       <c r="D44" t="n">
-        <v>3.5</v>
+        <v>3.83</v>
       </c>
       <c r="E44" t="n">
         <v>2</v>

--- a/docs/d/80/inyear.xlsx
+++ b/docs/d/80/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 24-Oct-2026. Built 2026-10-25 11:50 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>255 days remain until 30 June 2027, when these scores become final.</t>
+          <t>248 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 5 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (67 days) - 5 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (126 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 21 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (157 days) - 21 clubs short</t>
         </is>
       </c>
     </row>
@@ -1896,13 +1896,13 @@
         </is>
       </c>
       <c r="I12" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J12" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L12" s="7" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
         <v>0</v>
       </c>
       <c r="V12" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W12" s="9" t="n">
         <v>0</v>
@@ -2900,7 +2900,7 @@
         </is>
       </c>
       <c r="E22" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F22" s="6" t="n">
         <v>10</v>
@@ -2940,8 +2940,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P22" s="9" t="n">
-        <v>3</v>
+      <c r="P22" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q22" s="9" t="n">
         <v>0</v>
@@ -3462,7 +3462,7 @@
         </is>
       </c>
       <c r="P27" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q27" s="9" t="n">
         <v>0</v>
@@ -3800,8 +3800,8 @@
       <c r="W30" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X30" s="9" t="n">
-        <v>3</v>
+      <c r="X30" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y30" s="9" t="n">
         <v>0</v>
@@ -5008,7 +5008,7 @@
         <v>1</v>
       </c>
       <c r="Q42" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R42" s="9" t="n">
         <v>0</v>
@@ -6358,7 +6358,7 @@
         </is>
       </c>
       <c r="P55" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q55" s="10" t="n">
         <v>2</v>
@@ -6466,7 +6466,7 @@
         <v>0</v>
       </c>
       <c r="Q56" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R56" s="9" t="n">
         <v>0</v>
@@ -9364,13 +9364,13 @@
         </is>
       </c>
       <c r="I84" s="4" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J84" s="4" t="n">
         <v>53</v>
       </c>
       <c r="K84" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L84" s="4" t="inlineStr">
         <is>
@@ -9412,7 +9412,7 @@
         <v>4</v>
       </c>
       <c r="W84" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X84" s="10" t="n">
         <v>6</v>
@@ -9776,13 +9776,13 @@
         </is>
       </c>
       <c r="I88" s="4" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J88" s="4" t="n">
         <v>37</v>
       </c>
       <c r="K88" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L88" s="4" t="inlineStr">
         <is>
@@ -9982,13 +9982,13 @@
         </is>
       </c>
       <c r="I90" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J90" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K90" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L90" s="7" t="inlineStr">
         <is>
@@ -10027,7 +10027,7 @@
         <v>0</v>
       </c>
       <c r="V90" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W90" s="9" t="n">
         <v>0</v>
@@ -10174,7 +10174,7 @@
         </is>
       </c>
       <c r="E92" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F92" s="6" t="n">
         <v>10</v>
@@ -10229,8 +10229,8 @@
       <c r="T92" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U92" s="9" t="n">
-        <v>0</v>
+      <c r="U92" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V92" s="9" t="n">
         <v>3</v>
@@ -10897,7 +10897,7 @@
         </is>
       </c>
       <c r="E99" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F99" s="6" t="n">
         <v>10</v>
@@ -10946,8 +10946,8 @@
       <c r="R99" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S99" s="9" t="n">
-        <v>1</v>
+      <c r="S99" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T99" s="10" t="n">
         <v>1</v>
@@ -11212,7 +11212,7 @@
         </is>
       </c>
       <c r="E102" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F102" s="6" t="n">
         <v>10</v>
@@ -11252,8 +11252,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P102" s="9" t="n">
-        <v>3</v>
+      <c r="P102" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q102" s="9" t="n">
         <v>0</v>
@@ -11743,13 +11743,13 @@
         </is>
       </c>
       <c r="I107" s="4" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="J107" s="4" t="n">
         <v>109</v>
       </c>
       <c r="K107" s="4" t="n">
-        <v>-12</v>
+        <v>-9</v>
       </c>
       <c r="L107" s="4" t="inlineStr">
         <is>
@@ -11791,7 +11791,7 @@
         <v>4</v>
       </c>
       <c r="W107" s="10" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="X107" s="10" t="n">
         <v>4</v>
@@ -12598,7 +12598,7 @@
         </is>
       </c>
       <c r="P115" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q115" s="9" t="n">
         <v>1</v>
@@ -12613,7 +12613,7 @@
         <v>1</v>
       </c>
       <c r="U115" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V115" s="9" t="n">
         <v>0</v>
@@ -12676,13 +12676,13 @@
         </is>
       </c>
       <c r="I116" s="4" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J116" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K116" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L116" s="4" t="inlineStr">
         <is>
@@ -12724,7 +12724,7 @@
         <v>4</v>
       </c>
       <c r="W116" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X116" s="10" t="n">
         <v>7</v>
@@ -13504,13 +13504,13 @@
         </is>
       </c>
       <c r="I124" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J124" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K124" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L124" s="7" t="inlineStr">
         <is>
@@ -13632,7 +13632,7 @@
         </is>
       </c>
       <c r="P125" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q125" s="9" t="n">
         <v>1</v>
@@ -13916,13 +13916,13 @@
         </is>
       </c>
       <c r="I128" s="4" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J128" s="4" t="n">
         <v>61</v>
       </c>
       <c r="K128" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L128" s="4" t="inlineStr">
         <is>
@@ -13964,7 +13964,7 @@
         <v>4</v>
       </c>
       <c r="W128" s="10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X128" s="10" t="n">
         <v>6</v>
@@ -15198,7 +15198,7 @@
         <v>0</v>
       </c>
       <c r="Q140" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R140" s="9" t="n">
         <v>0</v>
@@ -16531,7 +16531,7 @@
         <v>2</v>
       </c>
       <c r="Q153" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R153" s="9" t="n">
         <v>0</v>
@@ -16592,7 +16592,7 @@
         </is>
       </c>
       <c r="E154" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F154" s="6" t="n">
         <v>10</v>
@@ -16606,13 +16606,13 @@
         </is>
       </c>
       <c r="I154" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J154" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K154" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L154" s="7" t="inlineStr">
         <is>
@@ -16650,8 +16650,8 @@
       <c r="U154" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="V154" s="9" t="n">
-        <v>3</v>
+      <c r="V154" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W154" s="9" t="n">
         <v>0</v>
@@ -16697,7 +16697,7 @@
         </is>
       </c>
       <c r="E155" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F155" s="6" t="n">
         <v>10</v>
@@ -16752,8 +16752,8 @@
       <c r="T155" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U155" s="9" t="n">
-        <v>0</v>
+      <c r="U155" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V155" s="9" t="n">
         <v>0</v>
@@ -16913,13 +16913,13 @@
         </is>
       </c>
       <c r="I157" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J157" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K157" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L157" s="7" t="inlineStr">
         <is>
@@ -16958,7 +16958,7 @@
         <v>0</v>
       </c>
       <c r="V157" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W157" s="9" t="n">
         <v>0</v>
@@ -17531,13 +17531,13 @@
         </is>
       </c>
       <c r="I163" s="4" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J163" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K163" s="4" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="L163" s="7" t="inlineStr">
         <is>
@@ -17579,7 +17579,7 @@
         <v>4</v>
       </c>
       <c r="W163" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X163" s="10" t="n">
         <v>6</v>
@@ -18088,7 +18088,7 @@
         <v>0</v>
       </c>
       <c r="S168" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T168" s="10" t="n">
         <v>1</v>
@@ -18153,13 +18153,13 @@
         </is>
       </c>
       <c r="I169" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J169" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K169" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L169" s="7" t="inlineStr">
         <is>
@@ -20447,13 +20447,13 @@
         </is>
       </c>
       <c r="I191" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J191" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K191" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L191" s="7" t="inlineStr">
         <is>
@@ -20492,7 +20492,7 @@
         <v>0</v>
       </c>
       <c r="V191" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W191" s="9" t="n">
         <v>0</v>
@@ -22549,7 +22549,7 @@
         <v>0</v>
       </c>
       <c r="S211" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T211" s="9" t="n">
         <v>0</v>
@@ -23030,13 +23030,13 @@
         </is>
       </c>
       <c r="I216" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J216" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K216" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L216" s="7" t="inlineStr">
         <is>
@@ -23078,7 +23078,7 @@
         <v>4</v>
       </c>
       <c r="W216" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X216" s="10" t="n">
         <v>4</v>
@@ -23131,13 +23131,13 @@
         </is>
       </c>
       <c r="I217" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J217" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K217" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L217" s="7" t="inlineStr">
         <is>
@@ -23176,7 +23176,7 @@
         <v>0</v>
       </c>
       <c r="V217" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W217" s="9" t="n">
         <v>0</v>
@@ -23657,7 +23657,7 @@
         <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="E7" t="n">
         <v>1</v>
@@ -24086,7 +24086,7 @@
         <v>5</v>
       </c>
       <c r="D20" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -24152,13 +24152,13 @@
         <v>4</v>
       </c>
       <c r="D22" t="n">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -24548,7 +24548,7 @@
         <v>5</v>
       </c>
       <c r="D34" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
